--- a/outputs/raw_data_cleaning/cleaned_raw_data_combined.xlsx
+++ b/outputs/raw_data_cleaning/cleaned_raw_data_combined.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rooms" sheetId="1" r:id="R16139a698ac94925"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff" sheetId="2" r:id="R683c3d42d83449f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="3" r:id="Ra9b76e442a9a4813"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="4" r:id="R93a35676ef2947c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Common Modules" sheetId="5" r:id="R6fe71cb5e8f04e78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Common Module Map" sheetId="6" r:id="R727f65e10ae6421f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded Rows" sheetId="7" r:id="R5c556704757a4a97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleanup Notes" sheetId="8" r:id="Rf45419825a9349e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rooms" sheetId="1" r:id="Rbc566847ba6b4980"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff" sheetId="2" r:id="R6ecdad78b7ad4036"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="3" r:id="R64ba38575a0949c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="4" r:id="Re584f4e2d09841ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Common Modules" sheetId="5" r:id="Re2e29e84f45a4733"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Common Module Map" sheetId="6" r:id="Red410997f5b54a2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded Rows" sheetId="7" r:id="Rdab94ed7111a4053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleanup Notes" sheetId="8" r:id="R5d6cb2ba38224e89"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -277,9 +277,9 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="36.75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="23.75" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="37.75" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="19.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.75" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="10.75" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12.75" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="13.75" hidden="0" customWidth="1"/>
@@ -311,22 +311,22 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="9" t="str">
-        <x:v>*SP-SR5A</x:v>
+        <x:v>CEFT External Venue</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>SP-SR5A</x:v>
+        <x:v>CEFT External Venue</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>External Venue</x:v>
       </x:c>
       <x:c r="D2" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E2" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="9" t="str">
-        <x:v>Physical</x:v>
+        <x:v>External</x:v>
       </x:c>
       <x:c r="G2" s="10" t="b">
         <x:v>0</x:v>
@@ -334,16 +334,16 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="9" t="str">
-        <x:v>*SP-SR5B</x:v>
+        <x:v>DV-AP-LT1A</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>SP-SR5B</x:v>
+        <x:v>DV-AP-LT1A</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D3" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E3" s="10" t="b">
         <x:v>0</x:v>
@@ -352,21 +352,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G3" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="9" t="str">
-        <x:v>*SP-SR5G</x:v>
+        <x:v>DV-AP-LT1B</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>SP-SR5G</x:v>
+        <x:v>DV-AP-LT1B</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D4" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E4" s="10" t="b">
         <x:v>0</x:v>
@@ -375,21 +375,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G4" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="9" t="str">
-        <x:v>*SP-SR5K</x:v>
+        <x:v>DV-AP-LT2A</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>SP-SR5K</x:v>
+        <x:v>DV-AP-LT2A</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D5" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E5" s="10" t="b">
         <x:v>0</x:v>
@@ -398,21 +398,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G5" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="9" t="str">
-        <x:v>*TP-SR3F</x:v>
+        <x:v>DV-AP-LT2B</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>TP-SR3F</x:v>
+        <x:v>DV-AP-LT2B</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D6" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E6" s="10" t="b">
         <x:v>0</x:v>
@@ -421,21 +421,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G6" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="9" t="str">
-        <x:v>*TP-SR3G</x:v>
+        <x:v>DV-AP-LT2C</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>TP-SR3G</x:v>
+        <x:v>DV-AP-LT2C</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D7" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="10" t="b">
         <x:v>0</x:v>
@@ -444,21 +444,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G7" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="9" t="str">
-        <x:v>*Temp Venue</x:v>
+        <x:v>DV-AP-LT2D</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>Temp Venue001</x:v>
+        <x:v>DV-AP-LT2D</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>Teaching Facility</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D8" s="9" t="n">
-        <x:v>999</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E8" s="10" t="b">
         <x:v>0</x:v>
@@ -467,44 +467,44 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G8" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="9" t="str">
-        <x:v>CEFT External Venue</x:v>
+        <x:v>DV-AP-LT2E</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>CEFT External Venue</x:v>
+        <x:v>DV-AP-LT2E</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>External Venue</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D9" s="9" t="n">
-        <x:v>200</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E9" s="10" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="9" t="str">
+        <x:v>Physical</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="b">
         <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9" s="9" t="str">
-        <x:v>External</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="b">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="9" t="str">
-        <x:v>DV-AP SR1M</x:v>
+        <x:v>DV-AP-SR1B</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>DV-AP-SR1M</x:v>
+        <x:v>DV-AP-SR1B</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D10" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E10" s="10" t="b">
         <x:v>0</x:v>
@@ -513,21 +513,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G10" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="9" t="str">
-        <x:v>DV-AP SR1S</x:v>
+        <x:v>DV-AP-SR1D</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>DV-AP-SR1S</x:v>
+        <x:v>DV-AP-SR1D</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D11" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E11" s="10" t="b">
         <x:v>0</x:v>
@@ -541,16 +541,16 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="9" t="str">
-        <x:v>DV-AP SR2H</x:v>
+        <x:v>DV-AP-SR1E</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>DV-AP-SR2H</x:v>
+        <x:v>DV-AP-SR1E</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D12" s="9" t="n">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E12" s="10" t="b">
         <x:v>0</x:v>
@@ -564,16 +564,16 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9" t="str">
-        <x:v>DV-AP SR4D</x:v>
+        <x:v>DV-AP-SR1H</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>DV-AP-SR4D</x:v>
+        <x:v>DV-AP-SR1H</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Laboratory</x:v>
       </x:c>
       <x:c r="D13" s="9" t="n">
-        <x:v>75</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E13" s="10" t="b">
         <x:v>0</x:v>
@@ -587,16 +587,16 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9" t="str">
-        <x:v>DV-AP SR4E</x:v>
+        <x:v>DV-AP-SR1L</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>DV-AP-SR4E</x:v>
+        <x:v>DV-AP-SR1L</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D14" s="9" t="n">
-        <x:v>90</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E14" s="10" t="b">
         <x:v>0</x:v>
@@ -605,21 +605,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G14" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="9" t="str">
-        <x:v>DV-AP SRB1F</x:v>
+        <x:v>DV-AP-SR1M</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>DV-AP-SRB1F</x:v>
+        <x:v>DV-AP SR1M</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D15" s="9" t="n">
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E15" s="10" t="b">
         <x:v>0</x:v>
@@ -628,18 +628,18 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G15" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="9" t="str">
-        <x:v>DV-AP-LT1A</x:v>
+        <x:v>DV-AP-SR1N</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>DV-AP-LT1A</x:v>
+        <x:v>DV-AP-SR1N</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D16" s="9" t="n">
         <x:v>49</x:v>
@@ -656,16 +656,16 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="9" t="str">
-        <x:v>DV-AP-LT1B</x:v>
+        <x:v>DV-AP-SR1P</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>DV-AP-LT1B</x:v>
+        <x:v>DV-AP-SR1P</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D17" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E17" s="10" t="b">
         <x:v>0</x:v>
@@ -674,21 +674,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G17" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="9" t="str">
-        <x:v>DV-AP-LT2A</x:v>
+        <x:v>DV-AP-SR1Q</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>DV-AP-LT2A</x:v>
+        <x:v>DV-AP-SR1Q</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D18" s="9" t="n">
-        <x:v>43</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E18" s="10" t="b">
         <x:v>0</x:v>
@@ -702,16 +702,16 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="9" t="str">
-        <x:v>DV-AP-LT2B</x:v>
+        <x:v>DV-AP-SR1R</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>DV-AP-LT2B</x:v>
+        <x:v>DV-AP-SR1R</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D19" s="9" t="n">
-        <x:v>44</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E19" s="10" t="b">
         <x:v>0</x:v>
@@ -725,16 +725,16 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="9" t="str">
-        <x:v>DV-AP-LT2C</x:v>
+        <x:v>DV-AP-SR1S</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>DV-AP-LT2C</x:v>
+        <x:v>DV-AP SR1S</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D20" s="9" t="n">
-        <x:v>36</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E20" s="10" t="b">
         <x:v>0</x:v>
@@ -743,21 +743,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G20" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="9" t="str">
-        <x:v>DV-AP-LT2D</x:v>
+        <x:v>DV-AP-SR1T</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>DV-AP-LT2D</x:v>
+        <x:v>DV-AP-SR1T</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D21" s="9" t="n">
-        <x:v>26</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E21" s="10" t="b">
         <x:v>0</x:v>
@@ -771,16 +771,16 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="9" t="str">
-        <x:v>DV-AP-LT2E</x:v>
+        <x:v>DV-AP-SR1U</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>DV-AP-LT2E</x:v>
+        <x:v>DV-AP-SR1U</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D22" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E22" s="10" t="b">
         <x:v>0</x:v>
@@ -794,16 +794,16 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="9" t="str">
-        <x:v>DV-AP-SR1B</x:v>
+        <x:v>DV-AP-SR2A</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>DV-AP-SR1B</x:v>
+        <x:v>DV-AP-SR2A</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D23" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E23" s="10" t="b">
         <x:v>0</x:v>
@@ -812,21 +812,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G23" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="9" t="str">
-        <x:v>DV-AP-SR1D</x:v>
+        <x:v>DV-AP-SR2B</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>DV-AP-SR1D</x:v>
+        <x:v>DV-AP-SR2B</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D24" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E24" s="10" t="b">
         <x:v>0</x:v>
@@ -835,21 +835,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G24" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="9" t="str">
-        <x:v>DV-AP-SR1E</x:v>
+        <x:v>DV-AP-SR2C</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>DV-AP-SR1E</x:v>
+        <x:v>DV-AP-SR2C</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D25" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E25" s="10" t="b">
         <x:v>0</x:v>
@@ -863,16 +863,16 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="9" t="str">
-        <x:v>DV-AP-SR1H</x:v>
+        <x:v>DV-AP-SR2D</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>DV-AP-SR1H</x:v>
+        <x:v>DV-AP-SR2D</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>Laboratory</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D26" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E26" s="10" t="b">
         <x:v>0</x:v>
@@ -886,16 +886,16 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="9" t="str">
-        <x:v>DV-AP-SR1L</x:v>
+        <x:v>DV-AP-SR2E</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>DV-AP-SR1L</x:v>
+        <x:v>DV-AP-SR2E</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D27" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E27" s="10" t="b">
         <x:v>0</x:v>
@@ -904,21 +904,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G27" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="9" t="str">
-        <x:v>DV-AP-SR1N</x:v>
+        <x:v>DV-AP-SR2F</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>DV-AP-SR1N</x:v>
+        <x:v>DV-AP-SR2F</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D28" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E28" s="10" t="b">
         <x:v>0</x:v>
@@ -927,21 +927,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G28" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="9" t="str">
-        <x:v>DV-AP-SR1P</x:v>
+        <x:v>DV-AP-SR2G</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>DV-AP-SR1P</x:v>
+        <x:v>DV-AP-SR2G</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D29" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E29" s="10" t="b">
         <x:v>0</x:v>
@@ -955,16 +955,16 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="9" t="str">
-        <x:v>DV-AP-SR1Q</x:v>
+        <x:v>DV-AP-SR2H</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>DV-AP-SR1Q</x:v>
+        <x:v>DV-AP SR2H</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D30" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E30" s="10" t="b">
         <x:v>0</x:v>
@@ -973,21 +973,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G30" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="9" t="str">
-        <x:v>DV-AP-SR1R</x:v>
+        <x:v>DV-AP-SR2J</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>DV-AP-SR1R</x:v>
+        <x:v>DV-AP-SR2J</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D31" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E31" s="10" t="b">
         <x:v>0</x:v>
@@ -1001,10 +1001,10 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="9" t="str">
-        <x:v>DV-AP-SR1T</x:v>
+        <x:v>DV-AP-SR2K</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>DV-AP-SR1T</x:v>
+        <x:v>DV-AP-SR2K</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -1024,16 +1024,16 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="9" t="str">
-        <x:v>DV-AP-SR1U</x:v>
+        <x:v>DV-AP-SR2L</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>DV-AP-SR1U</x:v>
+        <x:v>DV-AP-SR2L</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D33" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E33" s="10" t="b">
         <x:v>0</x:v>
@@ -1047,16 +1047,16 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="9" t="str">
-        <x:v>DV-AP-SR2A</x:v>
+        <x:v>DV-AP-SR2M</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>DV-AP-SR2A</x:v>
+        <x:v>DV-AP-SR2M</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D34" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E34" s="10" t="b">
         <x:v>0</x:v>
@@ -1070,16 +1070,16 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="9" t="str">
-        <x:v>DV-AP-SR2B</x:v>
+        <x:v>DV-AP-SR2N</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>DV-AP-SR2B</x:v>
+        <x:v>DV-AP-SR2N</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D35" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E35" s="10" t="b">
         <x:v>0</x:v>
@@ -1088,21 +1088,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G35" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="9" t="str">
-        <x:v>DV-AP-SR2C</x:v>
+        <x:v>DV-AP-SR2P</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>DV-AP-SR2C</x:v>
+        <x:v>DV-AP-SR2P</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D36" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E36" s="10" t="b">
         <x:v>0</x:v>
@@ -1111,21 +1111,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G36" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="9" t="str">
-        <x:v>DV-AP-SR2D</x:v>
+        <x:v>DV-AP-SR2Q</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>DV-AP-SR2D</x:v>
+        <x:v>DV-AP-SR2Q</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D37" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E37" s="10" t="b">
         <x:v>0</x:v>
@@ -1139,10 +1139,10 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="9" t="str">
-        <x:v>DV-AP-SR2E</x:v>
+        <x:v>DV-AP-SR2R</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>DV-AP-SR2E</x:v>
+        <x:v>DV-AP-SR2R</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -1162,16 +1162,16 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="9" t="str">
-        <x:v>DV-AP-SR2F</x:v>
+        <x:v>DV-AP-SR3A</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>DV-AP-SR2F</x:v>
+        <x:v>DV-AP-SR3A</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D39" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E39" s="10" t="b">
         <x:v>0</x:v>
@@ -1185,16 +1185,16 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="9" t="str">
-        <x:v>DV-AP-SR2G</x:v>
+        <x:v>DV-AP-SR3B</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>DV-AP-SR2G</x:v>
+        <x:v>DV-AP-SR3B</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D40" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E40" s="10" t="b">
         <x:v>0</x:v>
@@ -1208,10 +1208,10 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="9" t="str">
-        <x:v>DV-AP-SR2J</x:v>
+        <x:v>DV-AP-SR3C</x:v>
       </x:c>
       <x:c r="B41" s="9" t="str">
-        <x:v>DV-AP-SR2J</x:v>
+        <x:v>DV-AP-SR3C</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -1226,21 +1226,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G41" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="9" t="str">
-        <x:v>DV-AP-SR2K</x:v>
+        <x:v>DV-AP-SR3D</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>DV-AP-SR2K</x:v>
+        <x:v>DV-AP-SR3D</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D42" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E42" s="10" t="b">
         <x:v>0</x:v>
@@ -1249,21 +1249,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G42" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="9" t="str">
-        <x:v>DV-AP-SR2L</x:v>
+        <x:v>DV-AP-SR3E</x:v>
       </x:c>
       <x:c r="B43" s="9" t="str">
-        <x:v>DV-AP-SR2L</x:v>
+        <x:v>DV-AP-SR3E</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D43" s="9" t="n">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E43" s="10" t="b">
         <x:v>0</x:v>
@@ -1272,21 +1272,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G43" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="9" t="str">
-        <x:v>DV-AP-SR2M</x:v>
+        <x:v>DV-AP-SR3F</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>DV-AP-SR2M</x:v>
+        <x:v>DV-AP-SR3F</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D44" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E44" s="10" t="b">
         <x:v>0</x:v>
@@ -1295,21 +1295,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G44" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="9" t="str">
-        <x:v>DV-AP-SR2N</x:v>
+        <x:v>DV-AP-SR3G</x:v>
       </x:c>
       <x:c r="B45" s="9" t="str">
-        <x:v>DV-AP-SR2N</x:v>
+        <x:v>DV-AP-SR3G</x:v>
       </x:c>
       <x:c r="C45" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D45" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E45" s="10" t="b">
         <x:v>0</x:v>
@@ -1323,16 +1323,16 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="9" t="str">
-        <x:v>DV-AP-SR2P</x:v>
+        <x:v>DV-AP-SR3G-A</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>DV-AP-SR2P</x:v>
+        <x:v>DV-AP-SR3G-A</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D46" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E46" s="10" t="b">
         <x:v>0</x:v>
@@ -1341,21 +1341,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G46" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="9" t="str">
-        <x:v>DV-AP-SR2Q</x:v>
+        <x:v>DV-AP-SR3G-F</x:v>
       </x:c>
       <x:c r="B47" s="9" t="str">
-        <x:v>DV-AP-SR2Q</x:v>
+        <x:v>DV-AP-SR3G-F</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D47" s="9" t="n">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E47" s="10" t="b">
         <x:v>0</x:v>
@@ -1369,16 +1369,16 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="9" t="str">
-        <x:v>DV-AP-SR2R</x:v>
+        <x:v>DV-AP-SR3G-M</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>DV-AP-SR2R</x:v>
+        <x:v>DV-AP-SR3G-M</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D48" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E48" s="10" t="b">
         <x:v>0</x:v>
@@ -1392,16 +1392,16 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="9" t="str">
-        <x:v>DV-AP-SR3A</x:v>
+        <x:v>DV-AP-SR3H</x:v>
       </x:c>
       <x:c r="B49" s="9" t="str">
-        <x:v>DV-AP-SR3A</x:v>
+        <x:v>DV-AP-SR3H</x:v>
       </x:c>
       <x:c r="C49" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D49" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E49" s="10" t="b">
         <x:v>0</x:v>
@@ -1410,21 +1410,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G49" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="9" t="str">
-        <x:v>DV-AP-SR3B</x:v>
+        <x:v>DV-AP-SR3J</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>DV-AP-SR3B</x:v>
+        <x:v>DV-AP-SR3J</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D50" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E50" s="10" t="b">
         <x:v>0</x:v>
@@ -1438,16 +1438,16 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="9" t="str">
-        <x:v>DV-AP-SR3C</x:v>
+        <x:v>DV-AP-SR3K</x:v>
       </x:c>
       <x:c r="B51" s="9" t="str">
-        <x:v>DV-AP-SR3C</x:v>
+        <x:v>DV-AP-SR3K</x:v>
       </x:c>
       <x:c r="C51" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D51" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E51" s="10" t="b">
         <x:v>0</x:v>
@@ -1456,21 +1456,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G51" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="9" t="str">
-        <x:v>DV-AP-SR3D</x:v>
+        <x:v>DV-AP-SR3L</x:v>
       </x:c>
       <x:c r="B52" s="9" t="str">
-        <x:v>DV-AP-SR3D</x:v>
+        <x:v>DV-AP-SR3L</x:v>
       </x:c>
       <x:c r="C52" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D52" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E52" s="10" t="b">
         <x:v>0</x:v>
@@ -1479,21 +1479,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G52" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="9" t="str">
-        <x:v>DV-AP-SR3E</x:v>
+        <x:v>DV-AP-SR3M</x:v>
       </x:c>
       <x:c r="B53" s="9" t="str">
-        <x:v>DV-AP-SR3E</x:v>
+        <x:v>DV-AP-SR3M</x:v>
       </x:c>
       <x:c r="C53" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D53" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E53" s="10" t="b">
         <x:v>0</x:v>
@@ -1502,21 +1502,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G53" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="9" t="str">
-        <x:v>DV-AP-SR3F</x:v>
+        <x:v>DV-AP-SR3N</x:v>
       </x:c>
       <x:c r="B54" s="9" t="str">
-        <x:v>DV-AP-SR3F</x:v>
+        <x:v>DV-AP-SR3N</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D54" s="9" t="n">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E54" s="10" t="b">
         <x:v>0</x:v>
@@ -1525,21 +1525,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G54" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="9" t="str">
-        <x:v>DV-AP-SR3G</x:v>
+        <x:v>DV-AP-SR3P</x:v>
       </x:c>
       <x:c r="B55" s="9" t="str">
-        <x:v>DV-AP-SR3G</x:v>
+        <x:v>DV-AP-SR3P</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D55" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E55" s="10" t="b">
         <x:v>0</x:v>
@@ -1548,21 +1548,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G55" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="9" t="str">
-        <x:v>DV-AP-SR3G-A</x:v>
+        <x:v>DV-AP-SR4A</x:v>
       </x:c>
       <x:c r="B56" s="9" t="str">
-        <x:v>DV-AP-SR3G-A</x:v>
+        <x:v>DV-AP-SR4A</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Laboratory</x:v>
       </x:c>
       <x:c r="D56" s="9" t="n">
-        <x:v>99</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E56" s="10" t="b">
         <x:v>0</x:v>
@@ -1576,16 +1576,16 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="9" t="str">
-        <x:v>DV-AP-SR3G-F</x:v>
+        <x:v>DV-AP-SR4B</x:v>
       </x:c>
       <x:c r="B57" s="9" t="str">
-        <x:v>DV-AP-SR3G-F</x:v>
+        <x:v>DV-AP-SR4B</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Laboratory</x:v>
       </x:c>
       <x:c r="D57" s="9" t="n">
-        <x:v>47</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E57" s="10" t="b">
         <x:v>0</x:v>
@@ -1599,16 +1599,16 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="9" t="str">
-        <x:v>DV-AP-SR3G-M</x:v>
+        <x:v>DV-AP-SR4C</x:v>
       </x:c>
       <x:c r="B58" s="9" t="str">
-        <x:v>DV-AP-SR3G-M</x:v>
+        <x:v>DV-AP-SR4C</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Laboratory</x:v>
       </x:c>
       <x:c r="D58" s="9" t="n">
-        <x:v>47</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E58" s="10" t="b">
         <x:v>0</x:v>
@@ -1622,16 +1622,16 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="9" t="str">
-        <x:v>DV-AP-SR3H</x:v>
+        <x:v>DV-AP-SR4D</x:v>
       </x:c>
       <x:c r="B59" s="9" t="str">
-        <x:v>DV-AP-SR3H</x:v>
+        <x:v>DV-AP SR4D</x:v>
       </x:c>
       <x:c r="C59" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D59" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E59" s="10" t="b">
         <x:v>0</x:v>
@@ -1640,21 +1640,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G59" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="9" t="str">
-        <x:v>DV-AP-SR3J</x:v>
+        <x:v>DV-AP-SR4E</x:v>
       </x:c>
       <x:c r="B60" s="9" t="str">
-        <x:v>DV-AP-SR3J</x:v>
+        <x:v>DV-AP SR4E</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D60" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E60" s="10" t="b">
         <x:v>0</x:v>
@@ -1668,16 +1668,16 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="9" t="str">
-        <x:v>DV-AP-SR3K</x:v>
+        <x:v>DV-AP-SR4F</x:v>
       </x:c>
       <x:c r="B61" s="9" t="str">
-        <x:v>DV-AP-SR3K</x:v>
+        <x:v>DV-AP-SR4F</x:v>
       </x:c>
       <x:c r="C61" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D61" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E61" s="10" t="b">
         <x:v>0</x:v>
@@ -1686,21 +1686,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G61" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="9" t="str">
-        <x:v>DV-AP-SR3L</x:v>
+        <x:v>DV-AP-SRB1</x:v>
       </x:c>
       <x:c r="B62" s="9" t="str">
-        <x:v>DV-AP-SR3L</x:v>
+        <x:v>DV-AP-SRB1</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Laboratory</x:v>
       </x:c>
       <x:c r="D62" s="9" t="n">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E62" s="10" t="b">
         <x:v>0</x:v>
@@ -1709,21 +1709,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G62" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="9" t="str">
-        <x:v>DV-AP-SR3M</x:v>
+        <x:v>DV-AP-SRB1A</x:v>
       </x:c>
       <x:c r="B63" s="9" t="str">
-        <x:v>DV-AP-SR3M</x:v>
+        <x:v>DV-AP-SRB1A</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D63" s="9" t="n">
-        <x:v>48</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E63" s="10" t="b">
         <x:v>0</x:v>
@@ -1732,21 +1732,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G63" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="9" t="str">
-        <x:v>DV-AP-SR3N</x:v>
+        <x:v>DV-AP-SRB1B</x:v>
       </x:c>
       <x:c r="B64" s="9" t="str">
-        <x:v>DV-AP-SR3N</x:v>
+        <x:v>DV-AP-SRB1B</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Laboratory</x:v>
       </x:c>
       <x:c r="D64" s="9" t="n">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E64" s="10" t="b">
         <x:v>0</x:v>
@@ -1755,21 +1755,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G64" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="9" t="str">
-        <x:v>DV-AP-SR3P</x:v>
+        <x:v>DV-AP-SRB1C</x:v>
       </x:c>
       <x:c r="B65" s="9" t="str">
-        <x:v>DV-AP-SR3P</x:v>
+        <x:v>DV-AP-SRB1C</x:v>
       </x:c>
       <x:c r="C65" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Laboratory</x:v>
       </x:c>
       <x:c r="D65" s="9" t="n">
-        <x:v>48</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E65" s="10" t="b">
         <x:v>0</x:v>
@@ -1778,21 +1778,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G65" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="9" t="str">
-        <x:v>DV-AP-SR4A</x:v>
+        <x:v>DV-AP-SRB1D</x:v>
       </x:c>
       <x:c r="B66" s="9" t="str">
-        <x:v>DV-AP-SR4A</x:v>
+        <x:v>DV-AP-SRB1D</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>Laboratory</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D66" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E66" s="10" t="b">
         <x:v>0</x:v>
@@ -1806,16 +1806,16 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="9" t="str">
-        <x:v>DV-AP-SR4B</x:v>
+        <x:v>DV-AP-SRB1E</x:v>
       </x:c>
       <x:c r="B67" s="9" t="str">
-        <x:v>DV-AP-SR4B</x:v>
+        <x:v>DV-AP-SRB1E</x:v>
       </x:c>
       <x:c r="C67" s="9" t="str">
-        <x:v>Laboratory</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D67" s="9" t="n">
-        <x:v>207</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E67" s="10" t="b">
         <x:v>0</x:v>
@@ -1829,16 +1829,16 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="9" t="str">
-        <x:v>DV-AP-SR4C</x:v>
+        <x:v>DV-AP-SRB1F</x:v>
       </x:c>
       <x:c r="B68" s="9" t="str">
-        <x:v>DV-AP-SR4C</x:v>
+        <x:v>DV-AP SRB1F</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
-        <x:v>Laboratory</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D68" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E68" s="10" t="b">
         <x:v>0</x:v>
@@ -1852,16 +1852,16 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="9" t="str">
-        <x:v>DV-AP-SR4F</x:v>
+        <x:v>DV-AP-SRB1F-A</x:v>
       </x:c>
       <x:c r="B69" s="9" t="str">
-        <x:v>DV-AP-SR4F</x:v>
+        <x:v>DV-AP-SRB1F-A</x:v>
       </x:c>
       <x:c r="C69" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D69" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E69" s="10" t="b">
         <x:v>0</x:v>
@@ -1875,16 +1875,16 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="9" t="str">
-        <x:v>DV-AP-SRB1</x:v>
+        <x:v>DV-AP-SRB1F-B</x:v>
       </x:c>
       <x:c r="B70" s="9" t="str">
-        <x:v>DV-AP-SRB1</x:v>
+        <x:v>DV-AP-SRB1F-B</x:v>
       </x:c>
       <x:c r="C70" s="9" t="str">
-        <x:v>Laboratory</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D70" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E70" s="10" t="b">
         <x:v>0</x:v>
@@ -1898,16 +1898,16 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="9" t="str">
-        <x:v>DV-AP-SRB1A</x:v>
+        <x:v>DV-SHED-SR1A</x:v>
       </x:c>
       <x:c r="B71" s="9" t="str">
-        <x:v>DV-AP-SRB1A</x:v>
+        <x:v>DV-SHED-SR1A</x:v>
       </x:c>
       <x:c r="C71" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D71" s="9" t="n">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E71" s="10" t="b">
         <x:v>0</x:v>
@@ -1921,16 +1921,16 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="9" t="str">
-        <x:v>DV-AP-SRB1B</x:v>
+        <x:v>DV-SHED-SR1B</x:v>
       </x:c>
       <x:c r="B72" s="9" t="str">
-        <x:v>DV-AP-SRB1B</x:v>
+        <x:v>DV-SHED-SR1B</x:v>
       </x:c>
       <x:c r="C72" s="9" t="str">
-        <x:v>Laboratory</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D72" s="9" t="n">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E72" s="10" t="b">
         <x:v>0</x:v>
@@ -1944,16 +1944,16 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="9" t="str">
-        <x:v>DV-AP-SRB1C</x:v>
+        <x:v>DV-SHED-SR1C</x:v>
       </x:c>
       <x:c r="B73" s="9" t="str">
-        <x:v>DV-AP-SRB1C</x:v>
+        <x:v>DV-SHED-SR1C</x:v>
       </x:c>
       <x:c r="C73" s="9" t="str">
-        <x:v>Laboratory</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D73" s="9" t="n">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E73" s="10" t="b">
         <x:v>0</x:v>
@@ -1967,16 +1967,16 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="9" t="str">
-        <x:v>DV-AP-SRB1D</x:v>
+        <x:v>DV-SHED-SR1D</x:v>
       </x:c>
       <x:c r="B74" s="9" t="str">
-        <x:v>DV-AP-SRB1D</x:v>
+        <x:v>DV-SHED-SR1D</x:v>
       </x:c>
       <x:c r="C74" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D74" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E74" s="10" t="b">
         <x:v>0</x:v>
@@ -1990,16 +1990,16 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="9" t="str">
-        <x:v>DV-AP-SRB1E</x:v>
+        <x:v>DV-SHED-SR1E</x:v>
       </x:c>
       <x:c r="B75" s="9" t="str">
-        <x:v>DV-AP-SRB1E</x:v>
+        <x:v>DV-SHED-SR1E</x:v>
       </x:c>
       <x:c r="C75" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D75" s="9" t="n">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E75" s="10" t="b">
         <x:v>0</x:v>
@@ -2013,10 +2013,10 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="9" t="str">
-        <x:v>DV-AP-SRB1F-A</x:v>
+        <x:v>DV-SHED-SR1F</x:v>
       </x:c>
       <x:c r="B76" s="9" t="str">
-        <x:v>DV-AP-SRB1F-A</x:v>
+        <x:v>DV-SHED-SR1F</x:v>
       </x:c>
       <x:c r="C76" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -2036,16 +2036,16 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="9" t="str">
-        <x:v>DV-AP-SRB1F-B</x:v>
+        <x:v>DV-SHED-SR1G</x:v>
       </x:c>
       <x:c r="B77" s="9" t="str">
-        <x:v>DV-AP-SRB1F-B</x:v>
+        <x:v>DV-SHED-SR1G</x:v>
       </x:c>
       <x:c r="C77" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D77" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E77" s="10" t="b">
         <x:v>0</x:v>
@@ -2059,16 +2059,16 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="9" t="str">
-        <x:v>DV-SHED-SR1A</x:v>
+        <x:v>DV-SHED-SR1H</x:v>
       </x:c>
       <x:c r="B78" s="9" t="str">
-        <x:v>DV-SHED-SR1A</x:v>
+        <x:v>DV-SHED-SR1H</x:v>
       </x:c>
       <x:c r="C78" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D78" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E78" s="10" t="b">
         <x:v>0</x:v>
@@ -2082,16 +2082,16 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="9" t="str">
-        <x:v>DV-SHED-SR1B</x:v>
+        <x:v>DV-SHED-SR1J</x:v>
       </x:c>
       <x:c r="B79" s="9" t="str">
-        <x:v>DV-SHED-SR1B</x:v>
+        <x:v>DV-SHED-SR1J</x:v>
       </x:c>
       <x:c r="C79" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D79" s="9" t="n">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E79" s="10" t="b">
         <x:v>0</x:v>
@@ -2105,16 +2105,16 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="9" t="str">
-        <x:v>DV-SHED-SR1C</x:v>
+        <x:v>DV-SHED-SR1K</x:v>
       </x:c>
       <x:c r="B80" s="9" t="str">
-        <x:v>DV-SHED-SR1C</x:v>
+        <x:v>DV-SHED-SR1K</x:v>
       </x:c>
       <x:c r="C80" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D80" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E80" s="10" t="b">
         <x:v>0</x:v>
@@ -2128,16 +2128,16 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="9" t="str">
-        <x:v>DV-SHED-SR1D</x:v>
+        <x:v>DV-SHED-SR2A</x:v>
       </x:c>
       <x:c r="B81" s="9" t="str">
-        <x:v>DV-SHED-SR1D</x:v>
+        <x:v>DV-SHED-SR2A</x:v>
       </x:c>
       <x:c r="C81" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D81" s="9" t="n">
-        <x:v>60</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E81" s="10" t="b">
         <x:v>0</x:v>
@@ -2151,16 +2151,16 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="9" t="str">
-        <x:v>DV-SHED-SR1E</x:v>
+        <x:v>DV-SHED-SR2B</x:v>
       </x:c>
       <x:c r="B82" s="9" t="str">
-        <x:v>DV-SHED-SR1E</x:v>
+        <x:v>DV-SHED-SR2B</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D82" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E82" s="10" t="b">
         <x:v>0</x:v>
@@ -2174,16 +2174,16 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="9" t="str">
-        <x:v>DV-SHED-SR1F</x:v>
+        <x:v>DV-SHED-SR2C</x:v>
       </x:c>
       <x:c r="B83" s="9" t="str">
-        <x:v>DV-SHED-SR1F</x:v>
+        <x:v>DV-SHED-SR2C</x:v>
       </x:c>
       <x:c r="C83" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D83" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E83" s="10" t="b">
         <x:v>0</x:v>
@@ -2197,16 +2197,16 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="9" t="str">
-        <x:v>DV-SHED-SR1G</x:v>
+        <x:v>DV-SHED-SR2D</x:v>
       </x:c>
       <x:c r="B84" s="9" t="str">
-        <x:v>DV-SHED-SR1G</x:v>
+        <x:v>DV-SHED-SR2D</x:v>
       </x:c>
       <x:c r="C84" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D84" s="9" t="n">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E84" s="10" t="b">
         <x:v>0</x:v>
@@ -2220,16 +2220,16 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="9" t="str">
-        <x:v>DV-SHED-SR1H</x:v>
+        <x:v>DV-SHED-SR2E</x:v>
       </x:c>
       <x:c r="B85" s="9" t="str">
-        <x:v>DV-SHED-SR1H</x:v>
+        <x:v>DV-SHED-SR2E</x:v>
       </x:c>
       <x:c r="C85" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D85" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E85" s="10" t="b">
         <x:v>0</x:v>
@@ -2243,16 +2243,16 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="9" t="str">
-        <x:v>DV-SHED-SR1J</x:v>
+        <x:v>DV-SHED-SR2F</x:v>
       </x:c>
       <x:c r="B86" s="9" t="str">
-        <x:v>DV-SHED-SR1J</x:v>
+        <x:v>DV-SHED-SR2F</x:v>
       </x:c>
       <x:c r="C86" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D86" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E86" s="10" t="b">
         <x:v>0</x:v>
@@ -2266,16 +2266,16 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="9" t="str">
-        <x:v>DV-SHED-SR1K</x:v>
+        <x:v>DV-SHED-SR2G</x:v>
       </x:c>
       <x:c r="B87" s="9" t="str">
-        <x:v>DV-SHED-SR1K</x:v>
+        <x:v>DV-SHED-SR2G</x:v>
       </x:c>
       <x:c r="C87" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D87" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E87" s="10" t="b">
         <x:v>0</x:v>
@@ -2289,16 +2289,16 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="9" t="str">
-        <x:v>DV-SHED-SR2A</x:v>
+        <x:v>DV-URC-SR1A</x:v>
       </x:c>
       <x:c r="B88" s="9" t="str">
-        <x:v>DV-SHED-SR2A</x:v>
+        <x:v>DV-URC SR1A</x:v>
       </x:c>
       <x:c r="C88" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D88" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E88" s="10" t="b">
         <x:v>0</x:v>
@@ -2307,21 +2307,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G88" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="9" t="str">
-        <x:v>DV-SHED-SR2B</x:v>
+        <x:v>DV-URC-SR1B</x:v>
       </x:c>
       <x:c r="B89" s="9" t="str">
-        <x:v>DV-SHED-SR2B</x:v>
+        <x:v>DV-URC-SR1B</x:v>
       </x:c>
       <x:c r="C89" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D89" s="9" t="n">
-        <x:v>21</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E89" s="10" t="b">
         <x:v>0</x:v>
@@ -2330,21 +2330,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G89" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="9" t="str">
-        <x:v>DV-SHED-SR2C</x:v>
+        <x:v>DV-URC-SR1C</x:v>
       </x:c>
       <x:c r="B90" s="9" t="str">
-        <x:v>DV-SHED-SR2C</x:v>
+        <x:v>DV-URC-SR1C</x:v>
       </x:c>
       <x:c r="C90" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D90" s="9" t="n">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E90" s="10" t="b">
         <x:v>0</x:v>
@@ -2358,16 +2358,16 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="9" t="str">
-        <x:v>DV-SHED-SR2D</x:v>
+        <x:v>DV-URC-SR1D</x:v>
       </x:c>
       <x:c r="B91" s="9" t="str">
-        <x:v>DV-SHED-SR2D</x:v>
+        <x:v>DV-URC SR1D</x:v>
       </x:c>
       <x:c r="C91" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D91" s="9" t="n">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E91" s="10" t="b">
         <x:v>0</x:v>
@@ -2381,16 +2381,16 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="9" t="str">
-        <x:v>DV-SHED-SR2E</x:v>
+        <x:v>DV-URC-SR1E</x:v>
       </x:c>
       <x:c r="B92" s="9" t="str">
-        <x:v>DV-SHED-SR2E</x:v>
+        <x:v>DV-URC SR1E</x:v>
       </x:c>
       <x:c r="C92" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D92" s="9" t="n">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E92" s="10" t="b">
         <x:v>0</x:v>
@@ -2404,16 +2404,16 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="9" t="str">
-        <x:v>DV-SHED-SR2F</x:v>
+        <x:v>DV-URC-SR1F</x:v>
       </x:c>
       <x:c r="B93" s="9" t="str">
-        <x:v>DV-SHED-SR2F</x:v>
+        <x:v>DV-URC-SR1F</x:v>
       </x:c>
       <x:c r="C93" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D93" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E93" s="10" t="b">
         <x:v>0</x:v>
@@ -2427,16 +2427,16 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="9" t="str">
-        <x:v>DV-SHED-SR2G</x:v>
+        <x:v>DV-URC-SR1G</x:v>
       </x:c>
       <x:c r="B94" s="9" t="str">
-        <x:v>DV-SHED-SR2G</x:v>
+        <x:v>DV-URC-SR1G</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D94" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E94" s="10" t="b">
         <x:v>0</x:v>
@@ -2450,16 +2450,16 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="9" t="str">
-        <x:v>DV-URC SR1A</x:v>
+        <x:v>DV-USC-LT1A</x:v>
       </x:c>
       <x:c r="B95" s="9" t="str">
-        <x:v>DV-URC-SR1A</x:v>
+        <x:v>DV-USC-Singapore Hokkien Huay Kuan</x:v>
       </x:c>
       <x:c r="C95" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D95" s="9" t="n">
-        <x:v>5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E95" s="10" t="b">
         <x:v>0</x:v>
@@ -2473,16 +2473,16 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="9" t="str">
-        <x:v>DV-URC SR1D</x:v>
+        <x:v>DV-USC-SR1C</x:v>
       </x:c>
       <x:c r="B96" s="9" t="str">
-        <x:v>DV-URC-SR1D</x:v>
+        <x:v>DV-USC-SR1C</x:v>
       </x:c>
       <x:c r="C96" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D96" s="9" t="n">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E96" s="10" t="b">
         <x:v>0</x:v>
@@ -2491,21 +2491,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G96" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="9" t="str">
-        <x:v>DV-URC SR1E</x:v>
+        <x:v>DV-USC-SR1D</x:v>
       </x:c>
       <x:c r="B97" s="9" t="str">
-        <x:v>DV-URC-SR1E</x:v>
+        <x:v>DV-USC-SR1D</x:v>
       </x:c>
       <x:c r="C97" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D97" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E97" s="10" t="b">
         <x:v>0</x:v>
@@ -2514,21 +2514,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G97" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="9" t="str">
-        <x:v>DV-URC-SR1B</x:v>
+        <x:v>DV-USC-SR1E</x:v>
       </x:c>
       <x:c r="B98" s="9" t="str">
-        <x:v>DV-URC-SR1B</x:v>
+        <x:v>DV-USC-SR1E</x:v>
       </x:c>
       <x:c r="C98" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D98" s="9" t="n">
-        <x:v>60</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E98" s="10" t="b">
         <x:v>0</x:v>
@@ -2537,21 +2537,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G98" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="9" t="str">
-        <x:v>DV-URC-SR1C</x:v>
+        <x:v>DV-USC-SR1F</x:v>
       </x:c>
       <x:c r="B99" s="9" t="str">
-        <x:v>DV-URC-SR1C</x:v>
+        <x:v>DV-USC-SR1F</x:v>
       </x:c>
       <x:c r="C99" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D99" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E99" s="10" t="b">
         <x:v>0</x:v>
@@ -2565,16 +2565,16 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="9" t="str">
-        <x:v>DV-URC-SR1F</x:v>
+        <x:v>DV-USC-SR1G</x:v>
       </x:c>
       <x:c r="B100" s="9" t="str">
-        <x:v>DV-URC-SR1F</x:v>
+        <x:v>DV-USC-SR1G</x:v>
       </x:c>
       <x:c r="C100" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D100" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E100" s="10" t="b">
         <x:v>0</x:v>
@@ -2588,16 +2588,16 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="9" t="str">
-        <x:v>DV-URC-SR1G</x:v>
+        <x:v>DV-USC-SR2C</x:v>
       </x:c>
       <x:c r="B101" s="9" t="str">
-        <x:v>DV-URC-SR1G</x:v>
+        <x:v>DV-USC-SR2C</x:v>
       </x:c>
       <x:c r="C101" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D101" s="9" t="n">
-        <x:v>4</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E101" s="10" t="b">
         <x:v>0</x:v>
@@ -2606,21 +2606,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G101" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="9" t="str">
-        <x:v>DV-USC-SR1C</x:v>
+        <x:v>DV-USC-SR2D</x:v>
       </x:c>
       <x:c r="B102" s="9" t="str">
-        <x:v>DV-USC-SR1C</x:v>
+        <x:v>DV-USC-SR2D</x:v>
       </x:c>
       <x:c r="C102" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D102" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E102" s="10" t="b">
         <x:v>0</x:v>
@@ -2629,21 +2629,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G102" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="9" t="str">
-        <x:v>DV-USC-SR1D</x:v>
+        <x:v>DV-USC-SR2E</x:v>
       </x:c>
       <x:c r="B103" s="9" t="str">
-        <x:v>DV-USC-SR1D</x:v>
+        <x:v>DV-USC-SR2E</x:v>
       </x:c>
       <x:c r="C103" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D103" s="9" t="n">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E103" s="10" t="b">
         <x:v>0</x:v>
@@ -2652,21 +2652,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G103" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="9" t="str">
-        <x:v>DV-USC-SR1E</x:v>
+        <x:v>E2-01-01-Lectorial 6</x:v>
       </x:c>
       <x:c r="B104" s="9" t="str">
-        <x:v>DV-USC-SR1E</x:v>
+        <x:v>Lectorial 6 E2-01-01</x:v>
       </x:c>
       <x:c r="C104" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D104" s="9" t="n">
-        <x:v>10</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E104" s="10" t="b">
         <x:v>0</x:v>
@@ -2675,21 +2675,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G104" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="9" t="str">
-        <x:v>DV-USC-SR1F</x:v>
+        <x:v>E2-01-02-Lectorial 7</x:v>
       </x:c>
       <x:c r="B105" s="9" t="str">
-        <x:v>DV-USC-SR1F</x:v>
+        <x:v>Lectorial 7 E2-01-02</x:v>
       </x:c>
       <x:c r="C105" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D105" s="9" t="n">
-        <x:v>10</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E105" s="10" t="b">
         <x:v>0</x:v>
@@ -2698,21 +2698,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G105" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="9" t="str">
-        <x:v>DV-USC-SR1G</x:v>
+        <x:v>E2-02-01-Lectorial 9</x:v>
       </x:c>
       <x:c r="B106" s="9" t="str">
-        <x:v>DV-USC-SR1G</x:v>
+        <x:v>Lectorial 9 E2-02-01</x:v>
       </x:c>
       <x:c r="C106" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D106" s="9" t="n">
-        <x:v>10</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E106" s="10" t="b">
         <x:v>0</x:v>
@@ -2721,21 +2721,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G106" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="9" t="str">
-        <x:v>DV-USC-SR2C</x:v>
+        <x:v>E2-02-06-SR203</x:v>
       </x:c>
       <x:c r="B107" s="9" t="str">
-        <x:v>DV-USC-SR2C</x:v>
+        <x:v>Seminar Room E2-02-06</x:v>
       </x:c>
       <x:c r="C107" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D107" s="9" t="n">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E107" s="10" t="b">
         <x:v>0</x:v>
@@ -2744,21 +2744,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G107" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="9" t="str">
-        <x:v>DV-USC-SR2D</x:v>
+        <x:v>E2-02-07-SR204</x:v>
       </x:c>
       <x:c r="B108" s="9" t="str">
-        <x:v>DV-USC-SR2D</x:v>
+        <x:v>Seminar Room E2-02-07</x:v>
       </x:c>
       <x:c r="C108" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D108" s="9" t="n">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E108" s="10" t="b">
         <x:v>0</x:v>
@@ -2767,21 +2767,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G108" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="9" t="str">
-        <x:v>DV-USC-SR2E</x:v>
+        <x:v>E2-02-09-SR205</x:v>
       </x:c>
       <x:c r="B109" s="9" t="str">
-        <x:v>DV-USC-SR2E</x:v>
+        <x:v>Seminar Room E2-02-09</x:v>
       </x:c>
       <x:c r="C109" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D109" s="9" t="n">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E109" s="10" t="b">
         <x:v>0</x:v>
@@ -2790,21 +2790,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G109" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="9" t="str">
-        <x:v>DV-USC-Singapore Hokkien Huay Kuan</x:v>
+        <x:v>E2-02-14-Lectorial 10</x:v>
       </x:c>
       <x:c r="B110" s="9" t="str">
-        <x:v>DV-USC-LT1A</x:v>
+        <x:v>Lectorial 10 E2-02-14</x:v>
       </x:c>
       <x:c r="C110" s="9" t="str">
         <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D110" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E110" s="10" t="b">
         <x:v>0</x:v>
@@ -2818,16 +2818,16 @@
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="9" t="str">
-        <x:v>E2-01-01-Lectorial 6</x:v>
+        <x:v>E2-03-02-SR220</x:v>
       </x:c>
       <x:c r="B111" s="9" t="str">
-        <x:v>Lectorial 6 E2-01-01</x:v>
+        <x:v>Seminar Room E2-03-02</x:v>
       </x:c>
       <x:c r="C111" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D111" s="9" t="n">
-        <x:v>158</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E111" s="10" t="b">
         <x:v>0</x:v>
@@ -2841,16 +2841,16 @@
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="9" t="str">
-        <x:v>E2-01-02-Lectorial 7</x:v>
+        <x:v>E2-03-03-SR221</x:v>
       </x:c>
       <x:c r="B112" s="9" t="str">
-        <x:v>Lectorial 7 E2-01-02</x:v>
+        <x:v>Seminar Room E2-03-03</x:v>
       </x:c>
       <x:c r="C112" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D112" s="9" t="n">
-        <x:v>255</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E112" s="10" t="b">
         <x:v>0</x:v>
@@ -2859,21 +2859,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G112" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="9" t="str">
-        <x:v>E2-02-01-Lectorial 9</x:v>
+        <x:v>E2-03-04-SR222</x:v>
       </x:c>
       <x:c r="B113" s="9" t="str">
-        <x:v>Lectorial 9 E2-02-01</x:v>
+        <x:v>Seminar Room E2-03-04</x:v>
       </x:c>
       <x:c r="C113" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D113" s="9" t="n">
-        <x:v>160</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E113" s="10" t="b">
         <x:v>0</x:v>
@@ -2882,21 +2882,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G113" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="9" t="str">
-        <x:v>E2-02-06-SR203</x:v>
+        <x:v>E2-03-05-SR223</x:v>
       </x:c>
       <x:c r="B114" s="9" t="str">
-        <x:v>Seminar Room E2-02-06</x:v>
+        <x:v>Seminar Room E2-03-05</x:v>
       </x:c>
       <x:c r="C114" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D114" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E114" s="10" t="b">
         <x:v>0</x:v>
@@ -2905,21 +2905,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G114" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="9" t="str">
-        <x:v>E2-02-07-SR204</x:v>
+        <x:v>E2-03-06-SR224</x:v>
       </x:c>
       <x:c r="B115" s="9" t="str">
-        <x:v>Seminar Room E2-02-07</x:v>
+        <x:v>Seminar Room E2-03-06</x:v>
       </x:c>
       <x:c r="C115" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D115" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E115" s="10" t="b">
         <x:v>0</x:v>
@@ -2928,21 +2928,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G115" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="9" t="str">
-        <x:v>E2-02-09-SR205</x:v>
+        <x:v>E2-03-09-SR225</x:v>
       </x:c>
       <x:c r="B116" s="9" t="str">
-        <x:v>Seminar Room E2-02-09</x:v>
+        <x:v>Seminar Room E2-03-09</x:v>
       </x:c>
       <x:c r="C116" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D116" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E116" s="10" t="b">
         <x:v>0</x:v>
@@ -2951,21 +2951,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G116" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="9" t="str">
-        <x:v>E2-02-14-Lectorial 10</x:v>
+        <x:v>E2-03-18-SR230</x:v>
       </x:c>
       <x:c r="B117" s="9" t="str">
-        <x:v>Lectorial 10 E2-02-14</x:v>
+        <x:v>Seminar Room E2-03-18</x:v>
       </x:c>
       <x:c r="C117" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D117" s="9" t="n">
-        <x:v>245</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E117" s="10" t="b">
         <x:v>0</x:v>
@@ -2974,21 +2974,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G117" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="9" t="str">
-        <x:v>E2-03-02-SR220</x:v>
+        <x:v>E2-03-21-SR231</x:v>
       </x:c>
       <x:c r="B118" s="9" t="str">
-        <x:v>Seminar Room E2-03-02</x:v>
+        <x:v>Seminar Room E2-03-21</x:v>
       </x:c>
       <x:c r="C118" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D118" s="9" t="n">
-        <x:v>70</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E118" s="10" t="b">
         <x:v>0</x:v>
@@ -2997,21 +2997,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G118" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="9" t="str">
-        <x:v>E2-03-03-SR221</x:v>
+        <x:v>E2-04-02-SR232</x:v>
       </x:c>
       <x:c r="B119" s="9" t="str">
-        <x:v>Seminar Room E2-03-03</x:v>
+        <x:v>Seminar Room E2-04-02</x:v>
       </x:c>
       <x:c r="C119" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D119" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E119" s="10" t="b">
         <x:v>0</x:v>
@@ -3020,15 +3020,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G119" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="9" t="str">
-        <x:v>E2-03-04-SR222</x:v>
+        <x:v>E2-04-03-SR233</x:v>
       </x:c>
       <x:c r="B120" s="9" t="str">
-        <x:v>Seminar Room E2-03-04</x:v>
+        <x:v>Seminar Room E2-04-03</x:v>
       </x:c>
       <x:c r="C120" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3048,16 +3048,16 @@
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="9" t="str">
-        <x:v>E2-03-05-SR223</x:v>
+        <x:v>E2-04-04-SR234</x:v>
       </x:c>
       <x:c r="B121" s="9" t="str">
-        <x:v>Seminar Room E2-03-05</x:v>
+        <x:v>Seminar Room E2-04-04</x:v>
       </x:c>
       <x:c r="C121" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D121" s="9" t="n">
-        <x:v>70</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E121" s="10" t="b">
         <x:v>0</x:v>
@@ -3066,21 +3066,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G121" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="9" t="str">
-        <x:v>E2-03-06-SR224</x:v>
+        <x:v>E2-04-05-SR235</x:v>
       </x:c>
       <x:c r="B122" s="9" t="str">
-        <x:v>Seminar Room E2-03-06</x:v>
+        <x:v>Seminar Room E2-04-05</x:v>
       </x:c>
       <x:c r="C122" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D122" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E122" s="10" t="b">
         <x:v>0</x:v>
@@ -3089,15 +3089,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G122" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="9" t="str">
-        <x:v>E2-03-09-SR225</x:v>
+        <x:v>E2-04-07-SR236</x:v>
       </x:c>
       <x:c r="B123" s="9" t="str">
-        <x:v>Seminar Room E2-03-09</x:v>
+        <x:v>Seminar Room E2-04-07</x:v>
       </x:c>
       <x:c r="C123" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3117,10 +3117,10 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="9" t="str">
-        <x:v>E2-03-18-SR230</x:v>
+        <x:v>E2-04-10-SR237</x:v>
       </x:c>
       <x:c r="B124" s="9" t="str">
-        <x:v>Seminar Room E2-03-18</x:v>
+        <x:v>Seminar Room E2-04-10</x:v>
       </x:c>
       <x:c r="C124" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3140,10 +3140,10 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="9" t="str">
-        <x:v>E2-03-21-SR231</x:v>
+        <x:v>E2-04-19-SR242</x:v>
       </x:c>
       <x:c r="B125" s="9" t="str">
-        <x:v>Seminar Room E2-03-21</x:v>
+        <x:v>Seminar Room E2-04-19</x:v>
       </x:c>
       <x:c r="C125" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3163,16 +3163,16 @@
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="9" t="str">
-        <x:v>E2-04-02-SR232</x:v>
+        <x:v>E2-04-22-SR243</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>Seminar Room E2-04-02</x:v>
+        <x:v>Seminar Room E2-04-22</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D126" s="9" t="n">
-        <x:v>70</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E126" s="10" t="b">
         <x:v>0</x:v>
@@ -3181,15 +3181,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G126" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="9" t="str">
-        <x:v>E2-04-03-SR233</x:v>
+        <x:v>E2-05-09-SR247</x:v>
       </x:c>
       <x:c r="B127" s="9" t="str">
-        <x:v>Seminar Room E2-04-03</x:v>
+        <x:v>Seminar Room E2-05-09</x:v>
       </x:c>
       <x:c r="C127" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3209,16 +3209,16 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="9" t="str">
-        <x:v>E2-04-04-SR234</x:v>
+        <x:v>E2-05-10-SR248</x:v>
       </x:c>
       <x:c r="B128" s="9" t="str">
-        <x:v>Seminar Room E2-04-04</x:v>
+        <x:v>Seminar Room E2-05-10</x:v>
       </x:c>
       <x:c r="C128" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D128" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E128" s="10" t="b">
         <x:v>0</x:v>
@@ -3232,16 +3232,16 @@
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="9" t="str">
-        <x:v>E2-04-05-SR235</x:v>
+        <x:v>E2-05-11-SR249</x:v>
       </x:c>
       <x:c r="B129" s="9" t="str">
-        <x:v>Seminar Room E2-04-05</x:v>
+        <x:v>Seminar Room E2-05-11</x:v>
       </x:c>
       <x:c r="C129" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D129" s="9" t="n">
-        <x:v>70</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E129" s="10" t="b">
         <x:v>0</x:v>
@@ -3250,21 +3250,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G129" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="9" t="str">
-        <x:v>E2-04-07-SR236</x:v>
+        <x:v>E2-06-03-SR250</x:v>
       </x:c>
       <x:c r="B130" s="9" t="str">
-        <x:v>Seminar Room E2-04-07</x:v>
+        <x:v>Seminar Room E2-06-03</x:v>
       </x:c>
       <x:c r="C130" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D130" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E130" s="10" t="b">
         <x:v>0</x:v>
@@ -3278,16 +3278,16 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="9" t="str">
-        <x:v>E2-04-10-SR237</x:v>
+        <x:v>E2-06-04-SR251</x:v>
       </x:c>
       <x:c r="B131" s="9" t="str">
-        <x:v>Seminar Room E2-04-10</x:v>
+        <x:v>Seminar Room E2-06-04</x:v>
       </x:c>
       <x:c r="C131" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D131" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E131" s="10" t="b">
         <x:v>0</x:v>
@@ -3301,16 +3301,16 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="9" t="str">
-        <x:v>E2-04-19-SR242</x:v>
+        <x:v>E2-06-05-SR252</x:v>
       </x:c>
       <x:c r="B132" s="9" t="str">
-        <x:v>Seminar Room E2-04-19</x:v>
+        <x:v>Seminar Room E2-06-05</x:v>
       </x:c>
       <x:c r="C132" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D132" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E132" s="10" t="b">
         <x:v>0</x:v>
@@ -3319,15 +3319,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G132" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="9" t="str">
-        <x:v>E2-04-22-SR243</x:v>
+        <x:v>E2-06-07-SR253</x:v>
       </x:c>
       <x:c r="B133" s="9" t="str">
-        <x:v>Seminar Room E2-04-22</x:v>
+        <x:v>Seminar Room E2-06-07</x:v>
       </x:c>
       <x:c r="C133" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3347,16 +3347,16 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="9" t="str">
-        <x:v>E2-05-09-SR247</x:v>
+        <x:v>E2-06-08-SR254</x:v>
       </x:c>
       <x:c r="B134" s="9" t="str">
-        <x:v>Seminar Room E2-05-09</x:v>
+        <x:v>Seminar Room E2-06-08</x:v>
       </x:c>
       <x:c r="C134" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D134" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E134" s="10" t="b">
         <x:v>0</x:v>
@@ -3370,10 +3370,10 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="9" t="str">
-        <x:v>E2-05-10-SR248</x:v>
+        <x:v>E2-06-09-SR256</x:v>
       </x:c>
       <x:c r="B135" s="9" t="str">
-        <x:v>Seminar Room E2-05-10</x:v>
+        <x:v>Seminar Room E2-06-09</x:v>
       </x:c>
       <x:c r="C135" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3393,10 +3393,10 @@
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="9" t="str">
-        <x:v>E2-05-11-SR249</x:v>
+        <x:v>E2-06-10-SR257</x:v>
       </x:c>
       <x:c r="B136" s="9" t="str">
-        <x:v>Seminar Room E2-05-11</x:v>
+        <x:v>Seminar Room E2-06-10</x:v>
       </x:c>
       <x:c r="C136" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3416,16 +3416,16 @@
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="9" t="str">
-        <x:v>E2-06-03-SR250</x:v>
+        <x:v>E2-06-11-SR258</x:v>
       </x:c>
       <x:c r="B137" s="9" t="str">
-        <x:v>Seminar Room E2-06-03</x:v>
+        <x:v>Seminar Room E2-06-11</x:v>
       </x:c>
       <x:c r="C137" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D137" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E137" s="10" t="b">
         <x:v>0</x:v>
@@ -3439,16 +3439,16 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="9" t="str">
-        <x:v>E2-06-04-SR251</x:v>
+        <x:v>E2-07-01-SR259</x:v>
       </x:c>
       <x:c r="B138" s="9" t="str">
-        <x:v>Seminar Room E2-06-04</x:v>
+        <x:v>Computer Room E2-07-01</x:v>
       </x:c>
       <x:c r="C138" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Computer Room</x:v>
       </x:c>
       <x:c r="D138" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E138" s="10" t="b">
         <x:v>0</x:v>
@@ -3457,21 +3457,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G138" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="9" t="str">
-        <x:v>E2-06-05-SR252</x:v>
+        <x:v>E2-07-02-SR260</x:v>
       </x:c>
       <x:c r="B139" s="9" t="str">
-        <x:v>Seminar Room E2-06-05</x:v>
+        <x:v>Computer Room E2-07-02</x:v>
       </x:c>
       <x:c r="C139" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Computer Room</x:v>
       </x:c>
       <x:c r="D139" s="9" t="n">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E139" s="10" t="b">
         <x:v>0</x:v>
@@ -3485,16 +3485,16 @@
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="9" t="str">
-        <x:v>E2-06-07-SR253</x:v>
+        <x:v>E2-07-05-SR263</x:v>
       </x:c>
       <x:c r="B140" s="9" t="str">
-        <x:v>Seminar Room E2-06-07</x:v>
+        <x:v>Seminar Room E2-07-05</x:v>
       </x:c>
       <x:c r="C140" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D140" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E140" s="10" t="b">
         <x:v>0</x:v>
@@ -3503,21 +3503,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G140" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="9" t="str">
-        <x:v>E2-06-08-SR254</x:v>
+        <x:v>E2-07-06-SR264</x:v>
       </x:c>
       <x:c r="B141" s="9" t="str">
-        <x:v>Seminar Room E2-06-08</x:v>
+        <x:v>Seminar Room E2-07-06</x:v>
       </x:c>
       <x:c r="C141" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D141" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E141" s="10" t="b">
         <x:v>0</x:v>
@@ -3531,16 +3531,16 @@
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="9" t="str">
-        <x:v>E2-06-09-SR256</x:v>
+        <x:v>E2-07-07-SR265</x:v>
       </x:c>
       <x:c r="B142" s="9" t="str">
-        <x:v>Seminar Room E2-06-09</x:v>
+        <x:v>Seminar Room E2-07-07</x:v>
       </x:c>
       <x:c r="C142" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D142" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E142" s="10" t="b">
         <x:v>0</x:v>
@@ -3554,16 +3554,16 @@
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="9" t="str">
-        <x:v>E2-06-10-SR257</x:v>
+        <x:v>E2-07-08-SR266</x:v>
       </x:c>
       <x:c r="B143" s="9" t="str">
-        <x:v>Seminar Room E2-06-10</x:v>
+        <x:v>Seminar Room E2-07-08</x:v>
       </x:c>
       <x:c r="C143" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D143" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E143" s="10" t="b">
         <x:v>0</x:v>
@@ -3572,15 +3572,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G143" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="9" t="str">
-        <x:v>E2-06-11-SR258</x:v>
+        <x:v>E2-07-15-SR267</x:v>
       </x:c>
       <x:c r="B144" s="9" t="str">
-        <x:v>Seminar Room E2-06-11</x:v>
+        <x:v>Seminar Room E2-07-15</x:v>
       </x:c>
       <x:c r="C144" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3600,16 +3600,16 @@
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="9" t="str">
-        <x:v>E2-07-01-SR259</x:v>
+        <x:v>E2-07-16-SR268</x:v>
       </x:c>
       <x:c r="B145" s="9" t="str">
-        <x:v>Computer Room E2-07-01</x:v>
+        <x:v>Seminar Room E2-07-16</x:v>
       </x:c>
       <x:c r="C145" s="9" t="str">
-        <x:v>Computer Room</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D145" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E145" s="10" t="b">
         <x:v>0</x:v>
@@ -3618,21 +3618,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G145" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="9" t="str">
-        <x:v>E2-07-02-SR260</x:v>
+        <x:v>E2-07-17-SR269</x:v>
       </x:c>
       <x:c r="B146" s="9" t="str">
-        <x:v>Computer Room E2-07-02</x:v>
+        <x:v>Seminar Room E2-07-17</x:v>
       </x:c>
       <x:c r="C146" s="9" t="str">
-        <x:v>Computer Room</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D146" s="9" t="n">
-        <x:v>48</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E146" s="10" t="b">
         <x:v>0</x:v>
@@ -3641,21 +3641,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G146" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="9" t="str">
-        <x:v>E2-07-05-SR263</x:v>
+        <x:v>E2-08-01</x:v>
       </x:c>
       <x:c r="B147" s="9" t="str">
-        <x:v>Seminar Room E2-07-05</x:v>
+        <x:v>Business Analytics &amp; Technology Lab</x:v>
       </x:c>
       <x:c r="C147" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Laboratory</x:v>
       </x:c>
       <x:c r="D147" s="9" t="n">
-        <x:v>70</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E147" s="10" t="b">
         <x:v>0</x:v>
@@ -3669,16 +3669,16 @@
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="9" t="str">
-        <x:v>E2-07-06-SR264</x:v>
+        <x:v>E2-2M-02-SR210</x:v>
       </x:c>
       <x:c r="B148" s="9" t="str">
-        <x:v>Seminar Room E2-07-06</x:v>
+        <x:v>Seminar Room E2-2M-02</x:v>
       </x:c>
       <x:c r="C148" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D148" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E148" s="10" t="b">
         <x:v>0</x:v>
@@ -3687,15 +3687,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G148" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="9" t="str">
-        <x:v>E2-07-07-SR265</x:v>
+        <x:v>E2-2M-03-SR211</x:v>
       </x:c>
       <x:c r="B149" s="9" t="str">
-        <x:v>Seminar Room E2-07-07</x:v>
+        <x:v>Seminar Room E2-2M-03</x:v>
       </x:c>
       <x:c r="C149" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3715,16 +3715,16 @@
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="9" t="str">
-        <x:v>E2-07-08-SR266</x:v>
+        <x:v>E2-2M-04-SR212</x:v>
       </x:c>
       <x:c r="B150" s="9" t="str">
-        <x:v>Seminar Room E2-07-08</x:v>
+        <x:v>Seminar Room E2-2M-04</x:v>
       </x:c>
       <x:c r="C150" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D150" s="9" t="n">
-        <x:v>70</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E150" s="10" t="b">
         <x:v>0</x:v>
@@ -3733,21 +3733,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G150" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="9" t="str">
-        <x:v>E2-07-15-SR267</x:v>
+        <x:v>E2-2M-05-SR213</x:v>
       </x:c>
       <x:c r="B151" s="9" t="str">
-        <x:v>Seminar Room E2-07-15</x:v>
+        <x:v>Seminar Room E2-2M-05</x:v>
       </x:c>
       <x:c r="C151" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D151" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E151" s="10" t="b">
         <x:v>0</x:v>
@@ -3756,15 +3756,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G151" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="9" t="str">
-        <x:v>E2-07-16-SR268</x:v>
+        <x:v>E2-2M-06-SR214</x:v>
       </x:c>
       <x:c r="B152" s="9" t="str">
-        <x:v>Seminar Room E2-07-16</x:v>
+        <x:v>Seminar Room E2-2M-06</x:v>
       </x:c>
       <x:c r="C152" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3784,10 +3784,10 @@
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="9" t="str">
-        <x:v>E2-07-17-SR269</x:v>
+        <x:v>E2-2M-09-SR215</x:v>
       </x:c>
       <x:c r="B153" s="9" t="str">
-        <x:v>Seminar Room E2-07-17</x:v>
+        <x:v>Seminar Room E2-2M-09</x:v>
       </x:c>
       <x:c r="C153" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -3807,16 +3807,16 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="9" t="str">
-        <x:v>E2-08-01</x:v>
+        <x:v>E2-2M-14-SR218</x:v>
       </x:c>
       <x:c r="B154" s="9" t="str">
-        <x:v>Business Analytics &amp; Technology Lab</x:v>
+        <x:v>Seminar Room E2-2M-14</x:v>
       </x:c>
       <x:c r="C154" s="9" t="str">
-        <x:v>Laboratory</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D154" s="9" t="n">
-        <x:v>100</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E154" s="10" t="b">
         <x:v>0</x:v>
@@ -3825,21 +3825,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G154" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="9" t="str">
-        <x:v>E2-2M-02-SR210</x:v>
+        <x:v>E2-2M-17-SR219</x:v>
       </x:c>
       <x:c r="B155" s="9" t="str">
-        <x:v>Seminar Room E2-2M-02</x:v>
+        <x:v>Seminar Room E2-2M-17</x:v>
       </x:c>
       <x:c r="C155" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D155" s="9" t="n">
-        <x:v>70</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E155" s="10" t="b">
         <x:v>0</x:v>
@@ -3848,21 +3848,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G155" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="9" t="str">
-        <x:v>E2-2M-03-SR211</x:v>
+        <x:v>E3-01-01-Lectorial 8</x:v>
       </x:c>
       <x:c r="B156" s="9" t="str">
-        <x:v>Seminar Room E2-2M-03</x:v>
+        <x:v>Lectorial 8 E3-01-01</x:v>
       </x:c>
       <x:c r="C156" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D156" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E156" s="10" t="b">
         <x:v>0</x:v>
@@ -3871,21 +3871,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G156" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="9" t="str">
-        <x:v>E2-2M-04-SR212</x:v>
+        <x:v>E3-02-01-Auditorium</x:v>
       </x:c>
       <x:c r="B157" s="9" t="str">
-        <x:v>Seminar Room E2-2M-04</x:v>
+        <x:v>Auditorium E3-02-01</x:v>
       </x:c>
       <x:c r="C157" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Auditorium</x:v>
       </x:c>
       <x:c r="D157" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="E157" s="10" t="b">
         <x:v>0</x:v>
@@ -3899,16 +3899,16 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="9" t="str">
-        <x:v>E2-2M-05-SR213</x:v>
+        <x:v>E6-02-01-SR301</x:v>
       </x:c>
       <x:c r="B158" s="9" t="str">
-        <x:v>Seminar Room E2-2M-05</x:v>
+        <x:v>Seminar Room E6-02-01</x:v>
       </x:c>
       <x:c r="C158" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D158" s="9" t="n">
-        <x:v>70</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E158" s="10" t="b">
         <x:v>0</x:v>
@@ -3917,21 +3917,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G158" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="9" t="str">
-        <x:v>E2-2M-06-SR214</x:v>
+        <x:v>E6-02-02-SR302</x:v>
       </x:c>
       <x:c r="B159" s="9" t="str">
-        <x:v>Seminar Room E2-2M-06</x:v>
+        <x:v>Seminar Room E6-02-02</x:v>
       </x:c>
       <x:c r="C159" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D159" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E159" s="10" t="b">
         <x:v>0</x:v>
@@ -3940,21 +3940,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G159" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="9" t="str">
-        <x:v>E2-2M-09-SR215</x:v>
+        <x:v>E6-02-03-Lectorial 11</x:v>
       </x:c>
       <x:c r="B160" s="9" t="str">
-        <x:v>Seminar Room E2-2M-09</x:v>
+        <x:v>Lectorial 11 E6-02-03</x:v>
       </x:c>
       <x:c r="C160" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D160" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E160" s="10" t="b">
         <x:v>0</x:v>
@@ -3963,21 +3963,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G160" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="9" t="str">
-        <x:v>E2-2M-14-SR218</x:v>
+        <x:v>E6-02-04-SR303</x:v>
       </x:c>
       <x:c r="B161" s="9" t="str">
-        <x:v>Seminar Room E2-2M-14</x:v>
+        <x:v>Seminar Room E6-02-04</x:v>
       </x:c>
       <x:c r="C161" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D161" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E161" s="10" t="b">
         <x:v>0</x:v>
@@ -3991,10 +3991,10 @@
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="9" t="str">
-        <x:v>E2-2M-17-SR219</x:v>
+        <x:v>E6-02-05-SR304</x:v>
       </x:c>
       <x:c r="B162" s="9" t="str">
-        <x:v>Seminar Room E2-2M-17</x:v>
+        <x:v>Seminar Room E6-02-05</x:v>
       </x:c>
       <x:c r="C162" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -4014,16 +4014,16 @@
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="9" t="str">
-        <x:v>E3-01-01-Lectorial 8</x:v>
+        <x:v>E6-02-06-SR305</x:v>
       </x:c>
       <x:c r="B163" s="9" t="str">
-        <x:v>Lectorial 8 E3-01-01</x:v>
+        <x:v>Seminar Room E6-02-06</x:v>
       </x:c>
       <x:c r="C163" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D163" s="9" t="n">
-        <x:v>250</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E163" s="10" t="b">
         <x:v>0</x:v>
@@ -4032,21 +4032,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G163" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="9" t="str">
-        <x:v>E3-02-01-Auditorium</x:v>
+        <x:v>E6-02-07-SR306</x:v>
       </x:c>
       <x:c r="B164" s="9" t="str">
-        <x:v>Auditorium E3-02-01</x:v>
+        <x:v>Seminar Room E6-02-07</x:v>
       </x:c>
       <x:c r="C164" s="9" t="str">
-        <x:v>Auditorium</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D164" s="9" t="n">
-        <x:v>823</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E164" s="10" t="b">
         <x:v>0</x:v>
@@ -4060,10 +4060,10 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="9" t="str">
-        <x:v>E6-02-01-SR301</x:v>
+        <x:v>E6-02-08-SR307</x:v>
       </x:c>
       <x:c r="B165" s="9" t="str">
-        <x:v>Seminar Room E6-02-01</x:v>
+        <x:v>Seminar Room E6-02-08</x:v>
       </x:c>
       <x:c r="C165" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -4083,16 +4083,16 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="9" t="str">
-        <x:v>E6-02-02-SR302</x:v>
+        <x:v>E6-02-11-SR310</x:v>
       </x:c>
       <x:c r="B166" s="9" t="str">
-        <x:v>Seminar Room E6-02-02</x:v>
+        <x:v>Seminar Room E6-02-11</x:v>
       </x:c>
       <x:c r="C166" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D166" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E166" s="10" t="b">
         <x:v>0</x:v>
@@ -4101,21 +4101,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G166" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="9" t="str">
-        <x:v>E6-02-03-Lectorial 11</x:v>
+        <x:v>E6-02-12-SR311</x:v>
       </x:c>
       <x:c r="B167" s="9" t="str">
-        <x:v>Lectorial 11 E6-02-03</x:v>
+        <x:v>Seminar Room E6-02-12</x:v>
       </x:c>
       <x:c r="C167" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D167" s="9" t="n">
-        <x:v>160</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E167" s="10" t="b">
         <x:v>0</x:v>
@@ -4124,21 +4124,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G167" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="9" t="str">
-        <x:v>E6-02-04-SR303</x:v>
+        <x:v>E6-02-13-SR312</x:v>
       </x:c>
       <x:c r="B168" s="9" t="str">
-        <x:v>Seminar Room E6-02-04</x:v>
+        <x:v>Seminar Room E6-02-13</x:v>
       </x:c>
       <x:c r="C168" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D168" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E168" s="10" t="b">
         <x:v>0</x:v>
@@ -4152,10 +4152,10 @@
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="9" t="str">
-        <x:v>E6-02-05-SR304</x:v>
+        <x:v>E6-02-14-SR313</x:v>
       </x:c>
       <x:c r="B169" s="9" t="str">
-        <x:v>Seminar Room E6-02-05</x:v>
+        <x:v>Seminar Room E6-02-14</x:v>
       </x:c>
       <x:c r="C169" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -4175,10 +4175,10 @@
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="9" t="str">
-        <x:v>E6-02-06-SR305</x:v>
+        <x:v>E6-02-15-SR314</x:v>
       </x:c>
       <x:c r="B170" s="9" t="str">
-        <x:v>Seminar Room E6-02-06</x:v>
+        <x:v>Seminar Room E6-02-15</x:v>
       </x:c>
       <x:c r="C170" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -4198,10 +4198,10 @@
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="9" t="str">
-        <x:v>E6-02-07-SR306</x:v>
+        <x:v>E6-02-16-SR315</x:v>
       </x:c>
       <x:c r="B171" s="9" t="str">
-        <x:v>Seminar Room E6-02-07</x:v>
+        <x:v>Seminar Room E6-02-16</x:v>
       </x:c>
       <x:c r="C171" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -4221,16 +4221,16 @@
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="9" t="str">
-        <x:v>E6-02-08-SR307</x:v>
+        <x:v>E6-03-05-SR335</x:v>
       </x:c>
       <x:c r="B172" s="9" t="str">
-        <x:v>Seminar Room E6-02-08</x:v>
+        <x:v>Seminar Room E6-03-05</x:v>
       </x:c>
       <x:c r="C172" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D172" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E172" s="10" t="b">
         <x:v>0</x:v>
@@ -4239,21 +4239,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G172" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="9" t="str">
-        <x:v>E6-02-11-SR310</x:v>
+        <x:v>E6-03-07-SR336</x:v>
       </x:c>
       <x:c r="B173" s="9" t="str">
-        <x:v>Seminar Room E6-02-11</x:v>
+        <x:v>Case Study Room E6-03-07</x:v>
       </x:c>
       <x:c r="C173" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D173" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E173" s="10" t="b">
         <x:v>0</x:v>
@@ -4262,21 +4262,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G173" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="9" t="str">
-        <x:v>E6-02-12-SR311</x:v>
+        <x:v>E6-03-10-SR337</x:v>
       </x:c>
       <x:c r="B174" s="9" t="str">
-        <x:v>Seminar Room E6-02-12</x:v>
+        <x:v>Seminar Room E6-03-10</x:v>
       </x:c>
       <x:c r="C174" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D174" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E174" s="10" t="b">
         <x:v>0</x:v>
@@ -4290,16 +4290,16 @@
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="9" t="str">
-        <x:v>E6-02-13-SR312</x:v>
+        <x:v>E6-03-11-SR338</x:v>
       </x:c>
       <x:c r="B175" s="9" t="str">
-        <x:v>Seminar Room E6-02-13</x:v>
+        <x:v>Seminar Room E6-03-11</x:v>
       </x:c>
       <x:c r="C175" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D175" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E175" s="10" t="b">
         <x:v>0</x:v>
@@ -4308,21 +4308,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G175" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="9" t="str">
-        <x:v>E6-02-14-SR313</x:v>
+        <x:v>E6-03-13-SR340</x:v>
       </x:c>
       <x:c r="B176" s="9" t="str">
-        <x:v>Seminar Room E6-02-14</x:v>
+        <x:v>Seminar Room E6-03-13</x:v>
       </x:c>
       <x:c r="C176" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D176" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E176" s="10" t="b">
         <x:v>0</x:v>
@@ -4331,21 +4331,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G176" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="9" t="str">
-        <x:v>E6-02-15-SR314</x:v>
+        <x:v>E6-03-14-SR341</x:v>
       </x:c>
       <x:c r="B177" s="9" t="str">
-        <x:v>Seminar Room E6-02-15</x:v>
+        <x:v>Seminar Room E6-03-14</x:v>
       </x:c>
       <x:c r="C177" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D177" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E177" s="10" t="b">
         <x:v>0</x:v>
@@ -4354,21 +4354,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G177" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="9" t="str">
-        <x:v>E6-02-16-SR315</x:v>
+        <x:v>E6-03-15-SR342</x:v>
       </x:c>
       <x:c r="B178" s="9" t="str">
-        <x:v>Seminar Room E6-02-16</x:v>
+        <x:v>Seminar Room E6-03-15</x:v>
       </x:c>
       <x:c r="C178" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D178" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E178" s="10" t="b">
         <x:v>0</x:v>
@@ -4377,21 +4377,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G178" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="9" t="str">
-        <x:v>E6-03-05-SR335</x:v>
+        <x:v>E6-03-16-SR343</x:v>
       </x:c>
       <x:c r="B179" s="9" t="str">
-        <x:v>Seminar Room E6-03-05</x:v>
+        <x:v>Seminar Room E6-03-16</x:v>
       </x:c>
       <x:c r="C179" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D179" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E179" s="10" t="b">
         <x:v>0</x:v>
@@ -4405,16 +4405,16 @@
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="9" t="str">
-        <x:v>E6-03-07-SR336</x:v>
+        <x:v>E6-04-02-SR346</x:v>
       </x:c>
       <x:c r="B180" s="9" t="str">
-        <x:v>Case Study Room E6-03-07</x:v>
+        <x:v>Seminar Room E6-04-02</x:v>
       </x:c>
       <x:c r="C180" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D180" s="9" t="n">
-        <x:v>60</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E180" s="10" t="b">
         <x:v>0</x:v>
@@ -4423,21 +4423,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G180" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="9" t="str">
-        <x:v>E6-03-10-SR337</x:v>
+        <x:v>E6-04-04-SR347</x:v>
       </x:c>
       <x:c r="B181" s="9" t="str">
-        <x:v>Seminar Room E6-03-10</x:v>
+        <x:v>Seminar Room E6-04-04</x:v>
       </x:c>
       <x:c r="C181" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D181" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E181" s="10" t="b">
         <x:v>0</x:v>
@@ -4446,21 +4446,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G181" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="9" t="str">
-        <x:v>E6-03-11-SR338</x:v>
+        <x:v>E6-04-10-SR348</x:v>
       </x:c>
       <x:c r="B182" s="9" t="str">
-        <x:v>Seminar Room E6-03-11</x:v>
+        <x:v>Seminar Room E6-04-10</x:v>
       </x:c>
       <x:c r="C182" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D182" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E182" s="10" t="b">
         <x:v>0</x:v>
@@ -4469,21 +4469,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G182" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="9" t="str">
-        <x:v>E6-03-13-SR340</x:v>
+        <x:v>E6-04-11-SR349</x:v>
       </x:c>
       <x:c r="B183" s="9" t="str">
-        <x:v>Seminar Room E6-03-13</x:v>
+        <x:v>Seminar Room E6-04-11</x:v>
       </x:c>
       <x:c r="C183" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D183" s="9" t="n">
-        <x:v>90</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E183" s="10" t="b">
         <x:v>0</x:v>
@@ -4492,21 +4492,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G183" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="9" t="str">
-        <x:v>E6-03-14-SR341</x:v>
+        <x:v>E6-04-13-SR351</x:v>
       </x:c>
       <x:c r="B184" s="9" t="str">
-        <x:v>Seminar Room E6-03-14</x:v>
+        <x:v>Seminar Room E6-04-13</x:v>
       </x:c>
       <x:c r="C184" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D184" s="9" t="n">
-        <x:v>80</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E184" s="10" t="b">
         <x:v>0</x:v>
@@ -4520,10 +4520,10 @@
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="9" t="str">
-        <x:v>E6-03-15-SR342</x:v>
+        <x:v>E6-04-14-SR352</x:v>
       </x:c>
       <x:c r="B185" s="9" t="str">
-        <x:v>Seminar Room E6-03-15</x:v>
+        <x:v>Seminar Room E6-04-14</x:v>
       </x:c>
       <x:c r="C185" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -4543,16 +4543,16 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="9" t="str">
-        <x:v>E6-03-16-SR343</x:v>
+        <x:v>E6-04-15-SR353</x:v>
       </x:c>
       <x:c r="B186" s="9" t="str">
-        <x:v>Seminar Room E6-03-16</x:v>
+        <x:v>Seminar Room E6-04-15</x:v>
       </x:c>
       <x:c r="C186" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D186" s="9" t="n">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E186" s="10" t="b">
         <x:v>0</x:v>
@@ -4566,16 +4566,16 @@
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="9" t="str">
-        <x:v>E6-04-02-SR346</x:v>
+        <x:v>E6-04-16-SR354</x:v>
       </x:c>
       <x:c r="B187" s="9" t="str">
-        <x:v>Seminar Room E6-04-02</x:v>
+        <x:v>Seminar Room E6-04-16</x:v>
       </x:c>
       <x:c r="C187" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D187" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E187" s="10" t="b">
         <x:v>0</x:v>
@@ -4584,21 +4584,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G187" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="9" t="str">
-        <x:v>E6-04-04-SR347</x:v>
+        <x:v>E6-04-17-SR355</x:v>
       </x:c>
       <x:c r="B188" s="9" t="str">
-        <x:v>Seminar Room E6-04-04</x:v>
+        <x:v>Seminar Room E6-04-17</x:v>
       </x:c>
       <x:c r="C188" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D188" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E188" s="10" t="b">
         <x:v>0</x:v>
@@ -4607,15 +4607,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G188" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="9" t="str">
-        <x:v>E6-04-10-SR348</x:v>
+        <x:v>E6-04-18-SR356</x:v>
       </x:c>
       <x:c r="B189" s="9" t="str">
-        <x:v>Seminar Room E6-04-10</x:v>
+        <x:v>Seminar Room E6-04-18</x:v>
       </x:c>
       <x:c r="C189" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -4635,16 +4635,16 @@
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="9" t="str">
-        <x:v>E6-04-11-SR349</x:v>
+        <x:v>E6-05-01-SR357</x:v>
       </x:c>
       <x:c r="B190" s="9" t="str">
-        <x:v>Seminar Room E6-04-11</x:v>
+        <x:v>Seminar Room E6-05-01</x:v>
       </x:c>
       <x:c r="C190" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D190" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E190" s="10" t="b">
         <x:v>0</x:v>
@@ -4653,21 +4653,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G190" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="9" t="str">
-        <x:v>E6-04-13-SR351</x:v>
+        <x:v>E6-05-04-SR358</x:v>
       </x:c>
       <x:c r="B191" s="9" t="str">
-        <x:v>Seminar Room E6-04-13</x:v>
+        <x:v>Seminar Room E6-05-04</x:v>
       </x:c>
       <x:c r="C191" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D191" s="9" t="n">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E191" s="10" t="b">
         <x:v>0</x:v>
@@ -4681,16 +4681,16 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="9" t="str">
-        <x:v>E6-04-14-SR352</x:v>
+        <x:v>E6-05-05-SR359</x:v>
       </x:c>
       <x:c r="B192" s="9" t="str">
-        <x:v>Seminar Room E6-04-14</x:v>
+        <x:v>Seminar Room E6-05-05</x:v>
       </x:c>
       <x:c r="C192" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D192" s="9" t="n">
-        <x:v>80</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E192" s="10" t="b">
         <x:v>0</x:v>
@@ -4704,16 +4704,16 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="9" t="str">
-        <x:v>E6-04-15-SR353</x:v>
+        <x:v>E6-05-06-SR360</x:v>
       </x:c>
       <x:c r="B193" s="9" t="str">
-        <x:v>Seminar Room E6-04-15</x:v>
+        <x:v>Seminar Room E6-05-06</x:v>
       </x:c>
       <x:c r="C193" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D193" s="9" t="n">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E193" s="10" t="b">
         <x:v>0</x:v>
@@ -4722,21 +4722,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G193" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="9" t="str">
-        <x:v>E6-04-16-SR354</x:v>
+        <x:v>E6-05-07-SR361</x:v>
       </x:c>
       <x:c r="B194" s="9" t="str">
-        <x:v>Seminar Room E6-04-16</x:v>
+        <x:v>Seminar Room E6-05-07</x:v>
       </x:c>
       <x:c r="C194" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D194" s="9" t="n">
-        <x:v>90</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E194" s="10" t="b">
         <x:v>0</x:v>
@@ -4745,21 +4745,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G194" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="9" t="str">
-        <x:v>E6-04-17-SR355</x:v>
+        <x:v>E6-06-01-SR362</x:v>
       </x:c>
       <x:c r="B195" s="9" t="str">
-        <x:v>Seminar Room E6-04-17</x:v>
+        <x:v>Seminar Room E6-06-01</x:v>
       </x:c>
       <x:c r="C195" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D195" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E195" s="10" t="b">
         <x:v>0</x:v>
@@ -4768,21 +4768,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G195" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="9" t="str">
-        <x:v>E6-04-18-SR356</x:v>
+        <x:v>E6-07-01-SR363</x:v>
       </x:c>
       <x:c r="B196" s="9" t="str">
-        <x:v>Seminar Room E6-04-18</x:v>
+        <x:v>Seminar Room E6-07-01</x:v>
       </x:c>
       <x:c r="C196" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D196" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E196" s="10" t="b">
         <x:v>0</x:v>
@@ -4791,21 +4791,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G196" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="9" t="str">
-        <x:v>E6-05-01-SR357</x:v>
+        <x:v>E6-07-02-SR364</x:v>
       </x:c>
       <x:c r="B197" s="9" t="str">
-        <x:v>Seminar Room E6-05-01</x:v>
+        <x:v>Seminar Room E6-07-02</x:v>
       </x:c>
       <x:c r="C197" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D197" s="9" t="n">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E197" s="10" t="b">
         <x:v>0</x:v>
@@ -4814,21 +4814,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G197" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="9" t="str">
-        <x:v>E6-05-04-SR358</x:v>
+        <x:v>E6-08-01-SR365</x:v>
       </x:c>
       <x:c r="B198" s="9" t="str">
-        <x:v>Seminar Room E6-05-04</x:v>
+        <x:v>Seminar Room E6-08-01</x:v>
       </x:c>
       <x:c r="C198" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D198" s="9" t="n">
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E198" s="10" t="b">
         <x:v>0</x:v>
@@ -4842,16 +4842,16 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="9" t="str">
-        <x:v>E6-05-05-SR359</x:v>
+        <x:v>E6-09-02-SR367</x:v>
       </x:c>
       <x:c r="B199" s="9" t="str">
-        <x:v>Seminar Room E6-05-05</x:v>
+        <x:v>Seminar Room E6-09-02</x:v>
       </x:c>
       <x:c r="C199" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D199" s="9" t="n">
-        <x:v>90</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E199" s="10" t="b">
         <x:v>0</x:v>
@@ -4860,21 +4860,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G199" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="9" t="str">
-        <x:v>E6-05-06-SR360</x:v>
+        <x:v>E6-2M-01-SR318</x:v>
       </x:c>
       <x:c r="B200" s="9" t="str">
-        <x:v>Seminar Room E6-05-06</x:v>
+        <x:v>Seminar Room E6-2M-01</x:v>
       </x:c>
       <x:c r="C200" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D200" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E200" s="10" t="b">
         <x:v>0</x:v>
@@ -4888,16 +4888,16 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="9" t="str">
-        <x:v>E6-05-07-SR361</x:v>
+        <x:v>E6-2M-02-SR319</x:v>
       </x:c>
       <x:c r="B201" s="9" t="str">
-        <x:v>Seminar Room E6-05-07</x:v>
+        <x:v>Seminar Room E6-2M-02</x:v>
       </x:c>
       <x:c r="C201" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D201" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E201" s="10" t="b">
         <x:v>0</x:v>
@@ -4906,21 +4906,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G201" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="9" t="str">
-        <x:v>E6-06-01-SR362</x:v>
+        <x:v>E6-2M-09-SR320</x:v>
       </x:c>
       <x:c r="B202" s="9" t="str">
-        <x:v>Seminar Room E6-06-01</x:v>
+        <x:v>Seminar Room E6-2M-09</x:v>
       </x:c>
       <x:c r="C202" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D202" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E202" s="10" t="b">
         <x:v>0</x:v>
@@ -4929,21 +4929,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G202" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="9" t="str">
-        <x:v>E6-07-01-SR363</x:v>
+        <x:v>E6-2M-10-SR321</x:v>
       </x:c>
       <x:c r="B203" s="9" t="str">
-        <x:v>Seminar Room E6-07-01</x:v>
+        <x:v>Seminar Room E6-2M-10</x:v>
       </x:c>
       <x:c r="C203" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D203" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E203" s="10" t="b">
         <x:v>0</x:v>
@@ -4952,15 +4952,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G203" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="9" t="str">
-        <x:v>E6-07-02-SR364</x:v>
+        <x:v>E6-2M-11-SR322</x:v>
       </x:c>
       <x:c r="B204" s="9" t="str">
-        <x:v>Seminar Room E6-07-02</x:v>
+        <x:v>Seminar Room E6-2M-11</x:v>
       </x:c>
       <x:c r="C204" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -4980,16 +4980,16 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="9" t="str">
-        <x:v>E6-08-01-SR365</x:v>
+        <x:v>E6-2M-12-SR323</x:v>
       </x:c>
       <x:c r="B205" s="9" t="str">
-        <x:v>Seminar Room E6-08-01</x:v>
+        <x:v>Seminar Room E6-2M-12</x:v>
       </x:c>
       <x:c r="C205" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D205" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E205" s="10" t="b">
         <x:v>0</x:v>
@@ -5003,16 +5003,16 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="9" t="str">
-        <x:v>E6-09-02-SR367</x:v>
+        <x:v>E6-2M-14-SR325</x:v>
       </x:c>
       <x:c r="B206" s="9" t="str">
-        <x:v>Seminar Room E6-09-02</x:v>
+        <x:v>Seminar Room E6-2M-14</x:v>
       </x:c>
       <x:c r="C206" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D206" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E206" s="10" t="b">
         <x:v>0</x:v>
@@ -5026,16 +5026,16 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="9" t="str">
-        <x:v>E6-2M-01-SR318</x:v>
+        <x:v>E6-2M-15-SR326</x:v>
       </x:c>
       <x:c r="B207" s="9" t="str">
-        <x:v>Seminar Room E6-2M-01</x:v>
+        <x:v>Seminar Room E6-2M-15</x:v>
       </x:c>
       <x:c r="C207" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D207" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E207" s="10" t="b">
         <x:v>0</x:v>
@@ -5049,16 +5049,16 @@
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="9" t="str">
-        <x:v>E6-2M-02-SR319</x:v>
+        <x:v>E6-2M-16-SR327</x:v>
       </x:c>
       <x:c r="B208" s="9" t="str">
-        <x:v>Seminar Room E6-2M-02</x:v>
+        <x:v>Seminar Room E6-2M-16</x:v>
       </x:c>
       <x:c r="C208" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D208" s="9" t="n">
-        <x:v>60</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E208" s="10" t="b">
         <x:v>0</x:v>
@@ -5067,15 +5067,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G208" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="9" t="str">
-        <x:v>E6-2M-09-SR320</x:v>
+        <x:v>E6-2M-17-SR328</x:v>
       </x:c>
       <x:c r="B209" s="9" t="str">
-        <x:v>Seminar Room E6-2M-09</x:v>
+        <x:v>Seminar Room E6-2M-17</x:v>
       </x:c>
       <x:c r="C209" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -5095,10 +5095,10 @@
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="9" t="str">
-        <x:v>E6-2M-10-SR321</x:v>
+        <x:v>E6-2M-18-SR329</x:v>
       </x:c>
       <x:c r="B210" s="9" t="str">
-        <x:v>Seminar Room E6-2M-10</x:v>
+        <x:v>Seminar Room E6-2M-18</x:v>
       </x:c>
       <x:c r="C210" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -5118,10 +5118,10 @@
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="9" t="str">
-        <x:v>E6-2M-11-SR322</x:v>
+        <x:v>E6-2M-19-SR330</x:v>
       </x:c>
       <x:c r="B211" s="9" t="str">
-        <x:v>Seminar Room E6-2M-11</x:v>
+        <x:v>Seminar Room E6-2M-19</x:v>
       </x:c>
       <x:c r="C211" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -5141,16 +5141,16 @@
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="9" t="str">
-        <x:v>E6-2M-12-SR323</x:v>
+        <x:v>E6-2M-20-SR331</x:v>
       </x:c>
       <x:c r="B212" s="9" t="str">
-        <x:v>Seminar Room E6-2M-12</x:v>
+        <x:v>Seminar Room E6-2M-20</x:v>
       </x:c>
       <x:c r="C212" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D212" s="9" t="n">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E212" s="10" t="b">
         <x:v>0</x:v>
@@ -5159,21 +5159,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G212" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="9" t="str">
-        <x:v>E6-2M-14-SR325</x:v>
+        <x:v>ENG External Venue</x:v>
       </x:c>
       <x:c r="B213" s="9" t="str">
-        <x:v>Seminar Room E6-2M-14</x:v>
+        <x:v>ENG External Venue</x:v>
       </x:c>
       <x:c r="C213" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>External Venue</x:v>
       </x:c>
       <x:c r="D213" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E213" s="10" t="b">
         <x:v>0</x:v>
@@ -5187,16 +5187,16 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="9" t="str">
-        <x:v>E6-2M-15-SR326</x:v>
+        <x:v>HSS External Venue</x:v>
       </x:c>
       <x:c r="B214" s="9" t="str">
-        <x:v>Seminar Room E6-2M-15</x:v>
+        <x:v>HSS External Venue</x:v>
       </x:c>
       <x:c r="C214" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>External Venue</x:v>
       </x:c>
       <x:c r="D214" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E214" s="10" t="b">
         <x:v>0</x:v>
@@ -5210,16 +5210,16 @@
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="9" t="str">
-        <x:v>E6-2M-16-SR327</x:v>
+        <x:v>ICT External Venue</x:v>
       </x:c>
       <x:c r="B215" s="9" t="str">
-        <x:v>Seminar Room E6-2M-16</x:v>
+        <x:v>ICT External Venue</x:v>
       </x:c>
       <x:c r="C215" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>External Venue</x:v>
       </x:c>
       <x:c r="D215" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E215" s="10" t="b">
         <x:v>0</x:v>
@@ -5233,16 +5233,16 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="9" t="str">
-        <x:v>E6-2M-17-SR328</x:v>
+        <x:v>NP-06-06-01/02</x:v>
       </x:c>
       <x:c r="B216" s="9" t="str">
-        <x:v>Seminar Room E6-2M-17</x:v>
+        <x:v>NP-06-06-01/02</x:v>
       </x:c>
       <x:c r="C216" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Teaching Facility</x:v>
       </x:c>
       <x:c r="D216" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E216" s="10" t="b">
         <x:v>0</x:v>
@@ -5256,16 +5256,16 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="9" t="str">
-        <x:v>E6-2M-18-SR329</x:v>
+        <x:v>NP-47-04-04</x:v>
       </x:c>
       <x:c r="B217" s="9" t="str">
-        <x:v>Seminar Room E6-2M-18</x:v>
+        <x:v>NP-47-04-04</x:v>
       </x:c>
       <x:c r="C217" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Teaching Facility</x:v>
       </x:c>
       <x:c r="D217" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E217" s="10" t="b">
         <x:v>0</x:v>
@@ -5279,16 +5279,16 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="9" t="str">
-        <x:v>E6-2M-19-SR330</x:v>
+        <x:v>NP-47-05-06/08</x:v>
       </x:c>
       <x:c r="B218" s="9" t="str">
-        <x:v>Seminar Room E6-2M-19</x:v>
+        <x:v>NP-47-05-06/08</x:v>
       </x:c>
       <x:c r="C218" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Teaching Facility</x:v>
       </x:c>
       <x:c r="D218" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E218" s="10" t="b">
         <x:v>0</x:v>
@@ -5302,16 +5302,16 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="9" t="str">
-        <x:v>E6-2M-20-SR331</x:v>
+        <x:v>NP-LT7A</x:v>
       </x:c>
       <x:c r="B219" s="9" t="str">
-        <x:v>Seminar Room E6-2M-20</x:v>
+        <x:v>NP-LT7A</x:v>
       </x:c>
       <x:c r="C219" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D219" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E219" s="10" t="b">
         <x:v>0</x:v>
@@ -5320,21 +5320,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G219" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="9" t="str">
-        <x:v>ENG External Venue</x:v>
+        <x:v>NP-LTB1A</x:v>
       </x:c>
       <x:c r="B220" s="9" t="str">
-        <x:v>ENG External Venue</x:v>
+        <x:v>NP-LTB1A</x:v>
       </x:c>
       <x:c r="C220" s="9" t="str">
-        <x:v>External Venue</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D220" s="9" t="n">
-        <x:v>225</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E220" s="10" t="b">
         <x:v>0</x:v>
@@ -5343,21 +5343,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G220" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="9" t="str">
-        <x:v>HSS External Venue</x:v>
+        <x:v>NP-LTB1B</x:v>
       </x:c>
       <x:c r="B221" s="9" t="str">
-        <x:v>HSS External Venue</x:v>
+        <x:v>NP-LTB1B</x:v>
       </x:c>
       <x:c r="C221" s="9" t="str">
-        <x:v>External Venue</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D221" s="9" t="n">
-        <x:v>500</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E221" s="10" t="b">
         <x:v>0</x:v>
@@ -5366,21 +5366,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G221" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="9" t="str">
-        <x:v>ICT External Venue</x:v>
+        <x:v>NP-LTB1C</x:v>
       </x:c>
       <x:c r="B222" s="9" t="str">
-        <x:v>ICT External Venue</x:v>
+        <x:v>NP-LTB1C</x:v>
       </x:c>
       <x:c r="C222" s="9" t="str">
-        <x:v>External Venue</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D222" s="9" t="n">
-        <x:v>100</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E222" s="10" t="b">
         <x:v>0</x:v>
@@ -5389,21 +5389,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G222" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="9" t="str">
-        <x:v>NP-06-06-01/02</x:v>
+        <x:v>NP-SR3A</x:v>
       </x:c>
       <x:c r="B223" s="9" t="str">
-        <x:v>NP-06-06-01/02</x:v>
+        <x:v>NP-SR3A</x:v>
       </x:c>
       <x:c r="C223" s="9" t="str">
-        <x:v>Teaching Facility</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D223" s="9" t="n">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E223" s="10" t="b">
         <x:v>0</x:v>
@@ -5412,21 +5412,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G223" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="9" t="str">
-        <x:v>NP-47-04-04</x:v>
+        <x:v>NP-SR3B</x:v>
       </x:c>
       <x:c r="B224" s="9" t="str">
-        <x:v>NP-47-04-04</x:v>
+        <x:v>NP-SR3B</x:v>
       </x:c>
       <x:c r="C224" s="9" t="str">
-        <x:v>Teaching Facility</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D224" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E224" s="10" t="b">
         <x:v>0</x:v>
@@ -5435,21 +5435,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G224" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="9" t="str">
-        <x:v>NP-47-05-06/08</x:v>
+        <x:v>NP-SR3C</x:v>
       </x:c>
       <x:c r="B225" s="9" t="str">
-        <x:v>NP-47-05-06/08</x:v>
+        <x:v>NP-SR3C</x:v>
       </x:c>
       <x:c r="C225" s="9" t="str">
-        <x:v>Teaching Facility</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D225" s="9" t="n">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E225" s="10" t="b">
         <x:v>0</x:v>
@@ -5458,21 +5458,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G225" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="9" t="str">
-        <x:v>NP-LT7A</x:v>
+        <x:v>NP-SR3D</x:v>
       </x:c>
       <x:c r="B226" s="9" t="str">
-        <x:v>NP-LT7A</x:v>
+        <x:v>NP-SR3D</x:v>
       </x:c>
       <x:c r="C226" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D226" s="9" t="n">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E226" s="10" t="b">
         <x:v>0</x:v>
@@ -5481,21 +5481,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G226" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="9" t="str">
-        <x:v>NP-LTB1A</x:v>
+        <x:v>NP-SR3E</x:v>
       </x:c>
       <x:c r="B227" s="9" t="str">
-        <x:v>NP-LTB1A</x:v>
+        <x:v>NP-SR3E</x:v>
       </x:c>
       <x:c r="C227" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D227" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E227" s="10" t="b">
         <x:v>0</x:v>
@@ -5504,21 +5504,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G227" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="9" t="str">
-        <x:v>NP-LTB1B</x:v>
+        <x:v>NP-SR3F</x:v>
       </x:c>
       <x:c r="B228" s="9" t="str">
-        <x:v>NP-LTB1B</x:v>
+        <x:v>NP-SR3F</x:v>
       </x:c>
       <x:c r="C228" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D228" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E228" s="10" t="b">
         <x:v>0</x:v>
@@ -5532,16 +5532,16 @@
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="9" t="str">
-        <x:v>NP-LTB1C</x:v>
+        <x:v>NP-SR3G</x:v>
       </x:c>
       <x:c r="B229" s="9" t="str">
-        <x:v>NP-LTB1C</x:v>
+        <x:v>NP-SR3G</x:v>
       </x:c>
       <x:c r="C229" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D229" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E229" s="10" t="b">
         <x:v>0</x:v>
@@ -5550,21 +5550,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G229" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="9" t="str">
-        <x:v>NP-SR3A</x:v>
+        <x:v>NP-SR3H</x:v>
       </x:c>
       <x:c r="B230" s="9" t="str">
-        <x:v>NP-SR3A</x:v>
+        <x:v>NP-SR3H</x:v>
       </x:c>
       <x:c r="C230" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D230" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E230" s="10" t="b">
         <x:v>0</x:v>
@@ -5573,21 +5573,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G230" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="9" t="str">
-        <x:v>NP-SR3B</x:v>
+        <x:v>NP-SR4A</x:v>
       </x:c>
       <x:c r="B231" s="9" t="str">
-        <x:v>NP-SR3B</x:v>
+        <x:v>NP-SR4A</x:v>
       </x:c>
       <x:c r="C231" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D231" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E231" s="10" t="b">
         <x:v>0</x:v>
@@ -5596,21 +5596,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G231" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="9" t="str">
-        <x:v>NP-SR3C</x:v>
+        <x:v>NP-SR4B</x:v>
       </x:c>
       <x:c r="B232" s="9" t="str">
-        <x:v>NP-SR3C</x:v>
+        <x:v>NP-SR4B</x:v>
       </x:c>
       <x:c r="C232" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D232" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E232" s="10" t="b">
         <x:v>0</x:v>
@@ -5619,21 +5619,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G232" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="9" t="str">
-        <x:v>NP-SR3D</x:v>
+        <x:v>NP-SR4C</x:v>
       </x:c>
       <x:c r="B233" s="9" t="str">
-        <x:v>NP-SR3D</x:v>
+        <x:v>NP-SR4C</x:v>
       </x:c>
       <x:c r="C233" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D233" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E233" s="10" t="b">
         <x:v>0</x:v>
@@ -5647,16 +5647,16 @@
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="9" t="str">
-        <x:v>NP-SR3E</x:v>
+        <x:v>NP-SR4D</x:v>
       </x:c>
       <x:c r="B234" s="9" t="str">
-        <x:v>NP-SR3E</x:v>
+        <x:v>NP-SR4D</x:v>
       </x:c>
       <x:c r="C234" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D234" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E234" s="10" t="b">
         <x:v>0</x:v>
@@ -5670,16 +5670,16 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="9" t="str">
-        <x:v>NP-SR3F</x:v>
+        <x:v>NP-SR4E</x:v>
       </x:c>
       <x:c r="B235" s="9" t="str">
-        <x:v>NP-SR3F</x:v>
+        <x:v>NP-SR4E</x:v>
       </x:c>
       <x:c r="C235" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D235" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E235" s="10" t="b">
         <x:v>0</x:v>
@@ -5688,21 +5688,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G235" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="9" t="str">
-        <x:v>NP-SR3G</x:v>
+        <x:v>NP-SR4F</x:v>
       </x:c>
       <x:c r="B236" s="9" t="str">
-        <x:v>NP-SR3G</x:v>
+        <x:v>NP-SR4F</x:v>
       </x:c>
       <x:c r="C236" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D236" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E236" s="10" t="b">
         <x:v>0</x:v>
@@ -5716,16 +5716,16 @@
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="9" t="str">
-        <x:v>NP-SR3H</x:v>
+        <x:v>NP-SR5A</x:v>
       </x:c>
       <x:c r="B237" s="9" t="str">
-        <x:v>NP-SR3H</x:v>
+        <x:v>NP-SR5A</x:v>
       </x:c>
       <x:c r="C237" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D237" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E237" s="10" t="b">
         <x:v>0</x:v>
@@ -5739,16 +5739,16 @@
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="9" t="str">
-        <x:v>NP-SR4A</x:v>
+        <x:v>NP-SR5B</x:v>
       </x:c>
       <x:c r="B238" s="9" t="str">
-        <x:v>NP-SR4A</x:v>
+        <x:v>NP-SR5B</x:v>
       </x:c>
       <x:c r="C238" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D238" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E238" s="10" t="b">
         <x:v>0</x:v>
@@ -5762,16 +5762,16 @@
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="9" t="str">
-        <x:v>NP-SR4B</x:v>
+        <x:v>NP-SR5C</x:v>
       </x:c>
       <x:c r="B239" s="9" t="str">
-        <x:v>NP-SR4B</x:v>
+        <x:v>NP-SR5C</x:v>
       </x:c>
       <x:c r="C239" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D239" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E239" s="10" t="b">
         <x:v>0</x:v>
@@ -5785,16 +5785,16 @@
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="9" t="str">
-        <x:v>NP-SR4C</x:v>
+        <x:v>NP-SR5D</x:v>
       </x:c>
       <x:c r="B240" s="9" t="str">
-        <x:v>NP-SR4C</x:v>
+        <x:v>NP-SR5D</x:v>
       </x:c>
       <x:c r="C240" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D240" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E240" s="10" t="b">
         <x:v>0</x:v>
@@ -5808,16 +5808,16 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="9" t="str">
-        <x:v>NP-SR4D</x:v>
+        <x:v>NP-SR6AB</x:v>
       </x:c>
       <x:c r="B241" s="9" t="str">
-        <x:v>NP-SR4D</x:v>
+        <x:v>NP-SR6AB</x:v>
       </x:c>
       <x:c r="C241" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D241" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E241" s="10" t="b">
         <x:v>0</x:v>
@@ -5826,21 +5826,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G241" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="9" t="str">
-        <x:v>NP-SR4E</x:v>
+        <x:v>NP-SR6C</x:v>
       </x:c>
       <x:c r="B242" s="9" t="str">
-        <x:v>NP-SR4E</x:v>
+        <x:v>NP-SR6C</x:v>
       </x:c>
       <x:c r="C242" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D242" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E242" s="10" t="b">
         <x:v>0</x:v>
@@ -5854,16 +5854,16 @@
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="9" t="str">
-        <x:v>NP-SR4F</x:v>
+        <x:v>NP-SR6D</x:v>
       </x:c>
       <x:c r="B243" s="9" t="str">
-        <x:v>NP-SR4F</x:v>
+        <x:v>NP-SR6D</x:v>
       </x:c>
       <x:c r="C243" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D243" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E243" s="10" t="b">
         <x:v>0</x:v>
@@ -5877,16 +5877,16 @@
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="9" t="str">
-        <x:v>NP-SR5A</x:v>
+        <x:v>NP-SR6E</x:v>
       </x:c>
       <x:c r="B244" s="9" t="str">
-        <x:v>NP-SR5A</x:v>
+        <x:v>NP-SR6E</x:v>
       </x:c>
       <x:c r="C244" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D244" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E244" s="10" t="b">
         <x:v>0</x:v>
@@ -5900,16 +5900,16 @@
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="9" t="str">
-        <x:v>NP-SR5B</x:v>
+        <x:v>NP-SR6F</x:v>
       </x:c>
       <x:c r="B245" s="9" t="str">
-        <x:v>NP-SR5B</x:v>
+        <x:v>NP-SR6F</x:v>
       </x:c>
       <x:c r="C245" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D245" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E245" s="10" t="b">
         <x:v>0</x:v>
@@ -5923,16 +5923,16 @@
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="9" t="str">
-        <x:v>NP-SR5C</x:v>
+        <x:v>NP-SR6G</x:v>
       </x:c>
       <x:c r="B246" s="9" t="str">
-        <x:v>NP-SR5C</x:v>
+        <x:v>NP-SR6G</x:v>
       </x:c>
       <x:c r="C246" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D246" s="9" t="n">
-        <x:v>29</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E246" s="10" t="b">
         <x:v>0</x:v>
@@ -5946,16 +5946,16 @@
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="9" t="str">
-        <x:v>NP-SR5D</x:v>
+        <x:v>NP-SR7AB</x:v>
       </x:c>
       <x:c r="B247" s="9" t="str">
-        <x:v>NP-SR5D</x:v>
+        <x:v>NP-SR7AB</x:v>
       </x:c>
       <x:c r="C247" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D247" s="9" t="n">
-        <x:v>76</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E247" s="10" t="b">
         <x:v>0</x:v>
@@ -5964,21 +5964,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G247" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="9" t="str">
-        <x:v>NP-SR6AB</x:v>
+        <x:v>NP-SR7C</x:v>
       </x:c>
       <x:c r="B248" s="9" t="str">
-        <x:v>NP-SR6AB</x:v>
+        <x:v>NP-SR7C</x:v>
       </x:c>
       <x:c r="C248" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D248" s="9" t="n">
-        <x:v>47</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E248" s="10" t="b">
         <x:v>0</x:v>
@@ -5987,21 +5987,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G248" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="9" t="str">
-        <x:v>NP-SR6C</x:v>
+        <x:v>NP-SR7D</x:v>
       </x:c>
       <x:c r="B249" s="9" t="str">
-        <x:v>NP-SR6C</x:v>
+        <x:v>NP-SR7D</x:v>
       </x:c>
       <x:c r="C249" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D249" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E249" s="10" t="b">
         <x:v>0</x:v>
@@ -6015,16 +6015,16 @@
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="9" t="str">
-        <x:v>NP-SR6D</x:v>
+        <x:v>NP-SR7E</x:v>
       </x:c>
       <x:c r="B250" s="9" t="str">
-        <x:v>NP-SR6D</x:v>
+        <x:v>NP-SR7E</x:v>
       </x:c>
       <x:c r="C250" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D250" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E250" s="10" t="b">
         <x:v>0</x:v>
@@ -6033,21 +6033,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G250" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="9" t="str">
-        <x:v>NP-SR6E</x:v>
+        <x:v>NP-SR7F</x:v>
       </x:c>
       <x:c r="B251" s="9" t="str">
-        <x:v>NP-SR6E</x:v>
+        <x:v>NP-SR7F</x:v>
       </x:c>
       <x:c r="C251" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D251" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E251" s="10" t="b">
         <x:v>0</x:v>
@@ -6056,21 +6056,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G251" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="9" t="str">
-        <x:v>NP-SR6F</x:v>
+        <x:v>NP-SR7G</x:v>
       </x:c>
       <x:c r="B252" s="9" t="str">
-        <x:v>NP-SR6F</x:v>
+        <x:v>NP-SR7G</x:v>
       </x:c>
       <x:c r="C252" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D252" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E252" s="10" t="b">
         <x:v>0</x:v>
@@ -6084,16 +6084,16 @@
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="9" t="str">
-        <x:v>NP-SR6G</x:v>
+        <x:v>NP-SR8AB</x:v>
       </x:c>
       <x:c r="B253" s="9" t="str">
-        <x:v>NP-SR6G</x:v>
+        <x:v>NP-SR8AB</x:v>
       </x:c>
       <x:c r="C253" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D253" s="9" t="n">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E253" s="10" t="b">
         <x:v>0</x:v>
@@ -6107,16 +6107,16 @@
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="9" t="str">
-        <x:v>NP-SR7AB</x:v>
+        <x:v>NP-SR8CD</x:v>
       </x:c>
       <x:c r="B254" s="9" t="str">
-        <x:v>NP-SR7AB</x:v>
+        <x:v>NP-SR8CD</x:v>
       </x:c>
       <x:c r="C254" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D254" s="9" t="n">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E254" s="10" t="b">
         <x:v>0</x:v>
@@ -6125,21 +6125,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G254" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="9" t="str">
-        <x:v>NP-SR7C</x:v>
+        <x:v>NP-SR8E</x:v>
       </x:c>
       <x:c r="B255" s="9" t="str">
-        <x:v>NP-SR7C</x:v>
+        <x:v>NP-SR8E</x:v>
       </x:c>
       <x:c r="C255" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D255" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E255" s="10" t="b">
         <x:v>0</x:v>
@@ -6148,21 +6148,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G255" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="9" t="str">
-        <x:v>NP-SR7D</x:v>
+        <x:v>NP-SR8F</x:v>
       </x:c>
       <x:c r="B256" s="9" t="str">
-        <x:v>NP-SR7D</x:v>
+        <x:v>NP-SR8F</x:v>
       </x:c>
       <x:c r="C256" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D256" s="9" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E256" s="10" t="b">
         <x:v>0</x:v>
@@ -6176,16 +6176,16 @@
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="9" t="str">
-        <x:v>NP-SR7E</x:v>
+        <x:v>NP-SR9A</x:v>
       </x:c>
       <x:c r="B257" s="9" t="str">
-        <x:v>NP-SR7E</x:v>
+        <x:v>NP-SR9A</x:v>
       </x:c>
       <x:c r="C257" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D257" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E257" s="10" t="b">
         <x:v>0</x:v>
@@ -6194,21 +6194,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G257" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="9" t="str">
-        <x:v>NP-SR7F</x:v>
+        <x:v>NP-SR9B</x:v>
       </x:c>
       <x:c r="B258" s="9" t="str">
-        <x:v>NP-SR7F</x:v>
+        <x:v>NP-SR9B</x:v>
       </x:c>
       <x:c r="C258" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D258" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E258" s="10" t="b">
         <x:v>0</x:v>
@@ -6217,21 +6217,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G258" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="9" t="str">
-        <x:v>NP-SR7G</x:v>
+        <x:v>NP-SR9C</x:v>
       </x:c>
       <x:c r="B259" s="9" t="str">
-        <x:v>NP-SR7G</x:v>
+        <x:v>NP-SR9C</x:v>
       </x:c>
       <x:c r="C259" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D259" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E259" s="10" t="b">
         <x:v>0</x:v>
@@ -6240,21 +6240,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G259" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="9" t="str">
-        <x:v>NP-SR8AB</x:v>
+        <x:v>NP-SR9D</x:v>
       </x:c>
       <x:c r="B260" s="9" t="str">
-        <x:v>NP-SR8AB</x:v>
+        <x:v>NP-SR9D</x:v>
       </x:c>
       <x:c r="C260" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D260" s="9" t="n">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E260" s="10" t="b">
         <x:v>0</x:v>
@@ -6263,21 +6263,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G260" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="9" t="str">
-        <x:v>NP-SR8CD</x:v>
+        <x:v>NYP-Block-S.S33A</x:v>
       </x:c>
       <x:c r="B261" s="9" t="str">
-        <x:v>NP-SR8CD</x:v>
+        <x:v>NYP-Block-S.S33A</x:v>
       </x:c>
       <x:c r="C261" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Teaching Facility</x:v>
       </x:c>
       <x:c r="D261" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E261" s="10" t="b">
         <x:v>0</x:v>
@@ -6291,16 +6291,16 @@
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="9" t="str">
-        <x:v>NP-SR8E</x:v>
+        <x:v>NYP-LT1A</x:v>
       </x:c>
       <x:c r="B262" s="9" t="str">
-        <x:v>NP-SR8E</x:v>
+        <x:v>NYP-LT1A</x:v>
       </x:c>
       <x:c r="C262" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D262" s="9" t="n">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E262" s="10" t="b">
         <x:v>0</x:v>
@@ -6314,16 +6314,16 @@
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="9" t="str">
-        <x:v>NP-SR8F</x:v>
+        <x:v>NYP-LT2A</x:v>
       </x:c>
       <x:c r="B263" s="9" t="str">
-        <x:v>NP-SR8F</x:v>
+        <x:v>NYP-LT2A</x:v>
       </x:c>
       <x:c r="C263" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D263" s="9" t="n">
-        <x:v>12</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E263" s="10" t="b">
         <x:v>0</x:v>
@@ -6332,21 +6332,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G263" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="9" t="str">
-        <x:v>NP-SR9A</x:v>
+        <x:v>NYP-LT2B</x:v>
       </x:c>
       <x:c r="B264" s="9" t="str">
-        <x:v>NP-SR9A</x:v>
+        <x:v>NYP-LT2B</x:v>
       </x:c>
       <x:c r="C264" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D264" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E264" s="10" t="b">
         <x:v>0</x:v>
@@ -6355,18 +6355,18 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G264" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="9" t="str">
-        <x:v>NP-SR9B</x:v>
+        <x:v>NYP-LT3A</x:v>
       </x:c>
       <x:c r="B265" s="9" t="str">
-        <x:v>NP-SR9B</x:v>
+        <x:v>NYP-LT3A</x:v>
       </x:c>
       <x:c r="C265" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D265" s="9" t="n">
         <x:v>49</x:v>
@@ -6378,21 +6378,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G265" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="9" t="str">
-        <x:v>NP-SR9C</x:v>
+        <x:v>NYP-LT3B</x:v>
       </x:c>
       <x:c r="B266" s="9" t="str">
-        <x:v>NP-SR9C</x:v>
+        <x:v>NYP-LT3B</x:v>
       </x:c>
       <x:c r="C266" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D266" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E266" s="10" t="b">
         <x:v>0</x:v>
@@ -6406,16 +6406,16 @@
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="9" t="str">
-        <x:v>NP-SR9D</x:v>
+        <x:v>NYP-LT4A</x:v>
       </x:c>
       <x:c r="B267" s="9" t="str">
-        <x:v>NP-SR9D</x:v>
+        <x:v>NYP-LT4A</x:v>
       </x:c>
       <x:c r="C267" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D267" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E267" s="10" t="b">
         <x:v>0</x:v>
@@ -6429,16 +6429,16 @@
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="9" t="str">
-        <x:v>NYP-Block-S.S33A</x:v>
+        <x:v>NYP-SR2A</x:v>
       </x:c>
       <x:c r="B268" s="9" t="str">
-        <x:v>NYP-Block-S.S33A</x:v>
+        <x:v>NYP-L2 SR2A</x:v>
       </x:c>
       <x:c r="C268" s="9" t="str">
-        <x:v>Teaching Facility</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D268" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E268" s="10" t="b">
         <x:v>0</x:v>
@@ -6447,15 +6447,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G268" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="9" t="str">
-        <x:v>NYP-L2 SR2A</x:v>
+        <x:v>NYP-SR2B</x:v>
       </x:c>
       <x:c r="B269" s="9" t="str">
-        <x:v>NYP-SR2A</x:v>
+        <x:v>NYP-L2 SR2B</x:v>
       </x:c>
       <x:c r="C269" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -6475,10 +6475,10 @@
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="9" t="str">
-        <x:v>NYP-L2 SR2B</x:v>
+        <x:v>NYP-SR3A</x:v>
       </x:c>
       <x:c r="B270" s="9" t="str">
-        <x:v>NYP-SR2B</x:v>
+        <x:v>NYP-L3 SR3A</x:v>
       </x:c>
       <x:c r="C270" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -6493,15 +6493,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G270" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="9" t="str">
-        <x:v>NYP-L3 SR3A</x:v>
+        <x:v>NYP-SR3B</x:v>
       </x:c>
       <x:c r="B271" s="9" t="str">
-        <x:v>NYP-SR3A</x:v>
+        <x:v>NYP-L3 SR3B</x:v>
       </x:c>
       <x:c r="C271" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -6521,16 +6521,16 @@
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="9" t="str">
-        <x:v>NYP-L3 SR3B</x:v>
+        <x:v>NYP-SR3E</x:v>
       </x:c>
       <x:c r="B272" s="9" t="str">
-        <x:v>NYP-SR3B</x:v>
+        <x:v>NYP-SR3E</x:v>
       </x:c>
       <x:c r="C272" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D272" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E272" s="10" t="b">
         <x:v>0</x:v>
@@ -6544,16 +6544,16 @@
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="9" t="str">
-        <x:v>NYP-L5 SR5F</x:v>
+        <x:v>NYP-SR3F</x:v>
       </x:c>
       <x:c r="B273" s="9" t="str">
-        <x:v>NYP-SR5F</x:v>
+        <x:v>NYP-SR3F</x:v>
       </x:c>
       <x:c r="C273" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D273" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E273" s="10" t="b">
         <x:v>0</x:v>
@@ -6562,21 +6562,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G273" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="9" t="str">
-        <x:v>NYP-L7 SR7C</x:v>
+        <x:v>NYP-SR4A</x:v>
       </x:c>
       <x:c r="B274" s="9" t="str">
-        <x:v>NYP-SR7C</x:v>
+        <x:v>NYP-SR4A</x:v>
       </x:c>
       <x:c r="C274" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D274" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E274" s="10" t="b">
         <x:v>0</x:v>
@@ -6585,21 +6585,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G274" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="9" t="str">
-        <x:v>NYP-L7 SR7D</x:v>
+        <x:v>NYP-SR4B</x:v>
       </x:c>
       <x:c r="B275" s="9" t="str">
-        <x:v>NYP-SR7D</x:v>
+        <x:v>NYP-SR4B</x:v>
       </x:c>
       <x:c r="C275" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D275" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E275" s="10" t="b">
         <x:v>0</x:v>
@@ -6608,21 +6608,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G275" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="9" t="str">
-        <x:v>NYP-L7 SR7E</x:v>
+        <x:v>NYP-SR4C</x:v>
       </x:c>
       <x:c r="B276" s="9" t="str">
-        <x:v>NYP-SR7E</x:v>
+        <x:v>NYP-SR4C</x:v>
       </x:c>
       <x:c r="C276" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D276" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E276" s="10" t="b">
         <x:v>0</x:v>
@@ -6631,21 +6631,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G276" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="9" t="str">
-        <x:v>NYP-LT1A</x:v>
+        <x:v>NYP-SR4D</x:v>
       </x:c>
       <x:c r="B277" s="9" t="str">
-        <x:v>NYP-LT1A</x:v>
+        <x:v>NYP-SR4D</x:v>
       </x:c>
       <x:c r="C277" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D277" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E277" s="10" t="b">
         <x:v>0</x:v>
@@ -6654,21 +6654,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G277" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="9" t="str">
-        <x:v>NYP-LT2A</x:v>
+        <x:v>NYP-SR4E</x:v>
       </x:c>
       <x:c r="B278" s="9" t="str">
-        <x:v>NYP-LT2A</x:v>
+        <x:v>NYP-SR4E</x:v>
       </x:c>
       <x:c r="C278" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D278" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E278" s="10" t="b">
         <x:v>0</x:v>
@@ -6677,21 +6677,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G278" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="9" t="str">
-        <x:v>NYP-LT2B</x:v>
+        <x:v>NYP-SR4F</x:v>
       </x:c>
       <x:c r="B279" s="9" t="str">
-        <x:v>NYP-LT2B</x:v>
+        <x:v>NYP-SR4F</x:v>
       </x:c>
       <x:c r="C279" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D279" s="9" t="n">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E279" s="10" t="b">
         <x:v>0</x:v>
@@ -6705,16 +6705,16 @@
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="9" t="str">
-        <x:v>NYP-LT3A</x:v>
+        <x:v>NYP-SR4G</x:v>
       </x:c>
       <x:c r="B280" s="9" t="str">
-        <x:v>NYP-LT3A</x:v>
+        <x:v>NYP-SR4G</x:v>
       </x:c>
       <x:c r="C280" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D280" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E280" s="10" t="b">
         <x:v>0</x:v>
@@ -6728,16 +6728,16 @@
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="9" t="str">
-        <x:v>NYP-LT3B</x:v>
+        <x:v>NYP-SR4H</x:v>
       </x:c>
       <x:c r="B281" s="9" t="str">
-        <x:v>NYP-LT3B</x:v>
+        <x:v>NYP-SR4H</x:v>
       </x:c>
       <x:c r="C281" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D281" s="9" t="n">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E281" s="10" t="b">
         <x:v>0</x:v>
@@ -6751,16 +6751,16 @@
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="9" t="str">
-        <x:v>NYP-LT4A</x:v>
+        <x:v>NYP-SR5A</x:v>
       </x:c>
       <x:c r="B282" s="9" t="str">
-        <x:v>NYP-LT4A</x:v>
+        <x:v>NYP-SR5A</x:v>
       </x:c>
       <x:c r="C282" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D282" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E282" s="10" t="b">
         <x:v>0</x:v>
@@ -6769,15 +6769,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G282" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="9" t="str">
-        <x:v>NYP-SR3E</x:v>
+        <x:v>NYP-SR5B</x:v>
       </x:c>
       <x:c r="B283" s="9" t="str">
-        <x:v>NYP-SR3E</x:v>
+        <x:v>NYP-SR5B</x:v>
       </x:c>
       <x:c r="C283" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -6797,16 +6797,16 @@
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="9" t="str">
-        <x:v>NYP-SR3F</x:v>
+        <x:v>NYP-SR5C</x:v>
       </x:c>
       <x:c r="B284" s="9" t="str">
-        <x:v>NYP-SR3F</x:v>
+        <x:v>NYP-SR5C</x:v>
       </x:c>
       <x:c r="C284" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D284" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E284" s="10" t="b">
         <x:v>0</x:v>
@@ -6815,21 +6815,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G284" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="9" t="str">
-        <x:v>NYP-SR4A</x:v>
+        <x:v>NYP-SR5D</x:v>
       </x:c>
       <x:c r="B285" s="9" t="str">
-        <x:v>NYP-SR4A</x:v>
+        <x:v>NYP-SR5D</x:v>
       </x:c>
       <x:c r="C285" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D285" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E285" s="10" t="b">
         <x:v>0</x:v>
@@ -6838,21 +6838,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G285" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="9" t="str">
-        <x:v>NYP-SR4B</x:v>
+        <x:v>NYP-SR5E</x:v>
       </x:c>
       <x:c r="B286" s="9" t="str">
-        <x:v>NYP-SR4B</x:v>
+        <x:v>NYP-SR5E</x:v>
       </x:c>
       <x:c r="C286" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D286" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E286" s="10" t="b">
         <x:v>0</x:v>
@@ -6861,21 +6861,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G286" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="9" t="str">
-        <x:v>NYP-SR4C</x:v>
+        <x:v>NYP-SR5F</x:v>
       </x:c>
       <x:c r="B287" s="9" t="str">
-        <x:v>NYP-SR4C</x:v>
+        <x:v>NYP-L5 SR5F</x:v>
       </x:c>
       <x:c r="C287" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D287" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E287" s="10" t="b">
         <x:v>0</x:v>
@@ -6884,21 +6884,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G287" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="9" t="str">
-        <x:v>NYP-SR4D</x:v>
+        <x:v>NYP-SR5G</x:v>
       </x:c>
       <x:c r="B288" s="9" t="str">
-        <x:v>NYP-SR4D</x:v>
+        <x:v>NYP-SR5G</x:v>
       </x:c>
       <x:c r="C288" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D288" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E288" s="10" t="b">
         <x:v>0</x:v>
@@ -6912,16 +6912,16 @@
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="9" t="str">
-        <x:v>NYP-SR4E</x:v>
+        <x:v>NYP-SR5H</x:v>
       </x:c>
       <x:c r="B289" s="9" t="str">
-        <x:v>NYP-SR4E</x:v>
+        <x:v>NYP-SR5H</x:v>
       </x:c>
       <x:c r="C289" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D289" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E289" s="10" t="b">
         <x:v>0</x:v>
@@ -6935,16 +6935,16 @@
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="9" t="str">
-        <x:v>NYP-SR4F</x:v>
+        <x:v>NYP-SR6A</x:v>
       </x:c>
       <x:c r="B290" s="9" t="str">
-        <x:v>NYP-SR4F</x:v>
+        <x:v>NYP-SR6A</x:v>
       </x:c>
       <x:c r="C290" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D290" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E290" s="10" t="b">
         <x:v>0</x:v>
@@ -6958,16 +6958,16 @@
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="9" t="str">
-        <x:v>NYP-SR4G</x:v>
+        <x:v>NYP-SR6B</x:v>
       </x:c>
       <x:c r="B291" s="9" t="str">
-        <x:v>NYP-SR4G</x:v>
+        <x:v>NYP-SR6B</x:v>
       </x:c>
       <x:c r="C291" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D291" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E291" s="10" t="b">
         <x:v>0</x:v>
@@ -6976,15 +6976,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G291" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="9" t="str">
-        <x:v>NYP-SR4H</x:v>
+        <x:v>NYP-SR6C</x:v>
       </x:c>
       <x:c r="B292" s="9" t="str">
-        <x:v>NYP-SR4H</x:v>
+        <x:v>NYP-SR6C</x:v>
       </x:c>
       <x:c r="C292" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -7004,16 +7004,16 @@
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="9" t="str">
-        <x:v>NYP-SR5A</x:v>
+        <x:v>NYP-SR6D</x:v>
       </x:c>
       <x:c r="B293" s="9" t="str">
-        <x:v>NYP-SR5A</x:v>
+        <x:v>NYP-SR6D</x:v>
       </x:c>
       <x:c r="C293" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D293" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E293" s="10" t="b">
         <x:v>0</x:v>
@@ -7027,16 +7027,16 @@
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="9" t="str">
-        <x:v>NYP-SR5B</x:v>
+        <x:v>NYP-SR6E</x:v>
       </x:c>
       <x:c r="B294" s="9" t="str">
-        <x:v>NYP-SR5B</x:v>
+        <x:v>NYP-SR6E</x:v>
       </x:c>
       <x:c r="C294" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D294" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E294" s="10" t="b">
         <x:v>0</x:v>
@@ -7050,16 +7050,16 @@
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="9" t="str">
-        <x:v>NYP-SR5C</x:v>
+        <x:v>NYP-SR6F</x:v>
       </x:c>
       <x:c r="B295" s="9" t="str">
-        <x:v>NYP-SR5C</x:v>
+        <x:v>NYP-SR6F</x:v>
       </x:c>
       <x:c r="C295" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D295" s="9" t="n">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E295" s="10" t="b">
         <x:v>0</x:v>
@@ -7068,21 +7068,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G295" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="9" t="str">
-        <x:v>NYP-SR5D</x:v>
+        <x:v>NYP-SR6G</x:v>
       </x:c>
       <x:c r="B296" s="9" t="str">
-        <x:v>NYP-SR5D</x:v>
+        <x:v>NYP-SR6G</x:v>
       </x:c>
       <x:c r="C296" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D296" s="9" t="n">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E296" s="10" t="b">
         <x:v>0</x:v>
@@ -7096,16 +7096,16 @@
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="9" t="str">
-        <x:v>NYP-SR5E</x:v>
+        <x:v>NYP-SR6H</x:v>
       </x:c>
       <x:c r="B297" s="9" t="str">
-        <x:v>NYP-SR5E</x:v>
+        <x:v>NYP-SR6H</x:v>
       </x:c>
       <x:c r="C297" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D297" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E297" s="10" t="b">
         <x:v>0</x:v>
@@ -7119,16 +7119,16 @@
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="9" t="str">
-        <x:v>NYP-SR5G</x:v>
+        <x:v>NYP-SR7A</x:v>
       </x:c>
       <x:c r="B298" s="9" t="str">
-        <x:v>NYP-SR5G</x:v>
+        <x:v>NYP-SR7A</x:v>
       </x:c>
       <x:c r="C298" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D298" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E298" s="10" t="b">
         <x:v>0</x:v>
@@ -7137,15 +7137,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G298" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="9" t="str">
-        <x:v>NYP-SR5H</x:v>
+        <x:v>NYP-SR7B</x:v>
       </x:c>
       <x:c r="B299" s="9" t="str">
-        <x:v>NYP-SR5H</x:v>
+        <x:v>NYP-SR7B</x:v>
       </x:c>
       <x:c r="C299" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -7160,15 +7160,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G299" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="9" t="str">
-        <x:v>NYP-SR6A</x:v>
+        <x:v>NYP-SR7C</x:v>
       </x:c>
       <x:c r="B300" s="9" t="str">
-        <x:v>NYP-SR6A</x:v>
+        <x:v>NYP-L7 SR7C</x:v>
       </x:c>
       <x:c r="C300" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -7188,16 +7188,16 @@
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="9" t="str">
-        <x:v>NYP-SR6B</x:v>
+        <x:v>NYP-SR7D</x:v>
       </x:c>
       <x:c r="B301" s="9" t="str">
-        <x:v>NYP-SR6B</x:v>
+        <x:v>NYP-L7 SR7D</x:v>
       </x:c>
       <x:c r="C301" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D301" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E301" s="10" t="b">
         <x:v>0</x:v>
@@ -7206,15 +7206,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G301" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="9" t="str">
-        <x:v>NYP-SR6C</x:v>
+        <x:v>NYP-SR7E</x:v>
       </x:c>
       <x:c r="B302" s="9" t="str">
-        <x:v>NYP-SR6C</x:v>
+        <x:v>NYP-L7 SR7E</x:v>
       </x:c>
       <x:c r="C302" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -7234,16 +7234,16 @@
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="9" t="str">
-        <x:v>NYP-SR6D</x:v>
+        <x:v>Online</x:v>
       </x:c>
       <x:c r="B303" s="9" t="str">
-        <x:v>NYP-SR6D</x:v>
+        <x:v>Online</x:v>
       </x:c>
       <x:c r="C303" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Teaching Facility</x:v>
       </x:c>
       <x:c r="D303" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="E303" s="10" t="b">
         <x:v>0</x:v>
@@ -7257,16 +7257,16 @@
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="9" t="str">
-        <x:v>NYP-SR6E</x:v>
+        <x:v>RP-LT1A</x:v>
       </x:c>
       <x:c r="B304" s="9" t="str">
-        <x:v>NYP-SR6E</x:v>
+        <x:v>RP-LT1A</x:v>
       </x:c>
       <x:c r="C304" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D304" s="9" t="n">
-        <x:v>60</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E304" s="10" t="b">
         <x:v>0</x:v>
@@ -7275,21 +7275,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G304" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="9" t="str">
-        <x:v>NYP-SR6F</x:v>
+        <x:v>RP-LT1B</x:v>
       </x:c>
       <x:c r="B305" s="9" t="str">
-        <x:v>NYP-SR6F</x:v>
+        <x:v>RP-LT1B</x:v>
       </x:c>
       <x:c r="C305" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D305" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E305" s="10" t="b">
         <x:v>0</x:v>
@@ -7298,21 +7298,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G305" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="9" t="str">
-        <x:v>NYP-SR6G</x:v>
+        <x:v>RP-LT6A</x:v>
       </x:c>
       <x:c r="B306" s="9" t="str">
-        <x:v>NYP-SR6G</x:v>
+        <x:v>RP-LT6A</x:v>
       </x:c>
       <x:c r="C306" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D306" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E306" s="10" t="b">
         <x:v>0</x:v>
@@ -7326,16 +7326,16 @@
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="9" t="str">
-        <x:v>NYP-SR6H</x:v>
+        <x:v>RP-LT7A</x:v>
       </x:c>
       <x:c r="B307" s="9" t="str">
-        <x:v>NYP-SR6H</x:v>
+        <x:v>RP-LT7A</x:v>
       </x:c>
       <x:c r="C307" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D307" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E307" s="10" t="b">
         <x:v>0</x:v>
@@ -7349,16 +7349,16 @@
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="9" t="str">
-        <x:v>NYP-SR7A</x:v>
+        <x:v>RP-LT8A</x:v>
       </x:c>
       <x:c r="B308" s="9" t="str">
-        <x:v>NYP-SR7A</x:v>
+        <x:v>RP-LT8A</x:v>
       </x:c>
       <x:c r="C308" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D308" s="9" t="n">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E308" s="10" t="b">
         <x:v>0</x:v>
@@ -7372,10 +7372,10 @@
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="9" t="str">
-        <x:v>NYP-SR7B</x:v>
+        <x:v>RP-SR1A</x:v>
       </x:c>
       <x:c r="B309" s="9" t="str">
-        <x:v>NYP-SR7B</x:v>
+        <x:v>RP-SR1A</x:v>
       </x:c>
       <x:c r="C309" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -7390,21 +7390,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G309" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="9" t="str">
-        <x:v>Online</x:v>
+        <x:v>RP-SR5D1</x:v>
       </x:c>
       <x:c r="B310" s="9" t="str">
-        <x:v>Online</x:v>
+        <x:v>RP-SR5D1</x:v>
       </x:c>
       <x:c r="C310" s="9" t="str">
-        <x:v>Teaching Facility</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D310" s="9" t="n">
-        <x:v>9000</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E310" s="10" t="b">
         <x:v>0</x:v>
@@ -7418,16 +7418,16 @@
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="9" t="str">
-        <x:v>RP-LT1A</x:v>
+        <x:v>RP-SR5D2</x:v>
       </x:c>
       <x:c r="B311" s="9" t="str">
-        <x:v>RP-LT1A</x:v>
+        <x:v>RP-SR5D2</x:v>
       </x:c>
       <x:c r="C311" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D311" s="9" t="n">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E311" s="10" t="b">
         <x:v>0</x:v>
@@ -7436,21 +7436,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G311" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="9" t="str">
-        <x:v>RP-LT1B</x:v>
+        <x:v>RP-SR6A</x:v>
       </x:c>
       <x:c r="B312" s="9" t="str">
-        <x:v>RP-LT1B</x:v>
+        <x:v>RP-SR6A</x:v>
       </x:c>
       <x:c r="C312" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D312" s="9" t="n">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E312" s="10" t="b">
         <x:v>0</x:v>
@@ -7464,16 +7464,16 @@
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="9" t="str">
-        <x:v>RP-LT6A</x:v>
+        <x:v>RP-SR6B</x:v>
       </x:c>
       <x:c r="B313" s="9" t="str">
-        <x:v>RP-LT6A</x:v>
+        <x:v>RP-SR6B</x:v>
       </x:c>
       <x:c r="C313" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D313" s="9" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E313" s="10" t="b">
         <x:v>0</x:v>
@@ -7487,13 +7487,13 @@
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="9" t="str">
-        <x:v>RP-LT7A</x:v>
+        <x:v>RP-SR6C</x:v>
       </x:c>
       <x:c r="B314" s="9" t="str">
-        <x:v>RP-LT7A</x:v>
+        <x:v>RP-SR6C</x:v>
       </x:c>
       <x:c r="C314" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D314" s="9" t="n">
         <x:v>18</x:v>
@@ -7510,13 +7510,13 @@
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="9" t="str">
-        <x:v>RP-LT8A</x:v>
+        <x:v>RP-SR6D</x:v>
       </x:c>
       <x:c r="B315" s="9" t="str">
-        <x:v>RP-LT8A</x:v>
+        <x:v>RP-SR6D</x:v>
       </x:c>
       <x:c r="C315" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D315" s="9" t="n">
         <x:v>18</x:v>
@@ -7533,16 +7533,16 @@
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="9" t="str">
-        <x:v>RP-SR1A</x:v>
+        <x:v>RP-SR6E</x:v>
       </x:c>
       <x:c r="B316" s="9" t="str">
-        <x:v>RP-SR1A</x:v>
+        <x:v>RP-SR6E</x:v>
       </x:c>
       <x:c r="C316" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D316" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E316" s="10" t="b">
         <x:v>0</x:v>
@@ -7551,21 +7551,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G316" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="9" t="str">
-        <x:v>RP-SR5D1</x:v>
+        <x:v>RP-SR6F</x:v>
       </x:c>
       <x:c r="B317" s="9" t="str">
-        <x:v>RP-SR5D1</x:v>
+        <x:v>RP-SR6F</x:v>
       </x:c>
       <x:c r="C317" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D317" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E317" s="10" t="b">
         <x:v>0</x:v>
@@ -7574,21 +7574,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G317" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="9" t="str">
-        <x:v>RP-SR5D2</x:v>
+        <x:v>RP-SR7A</x:v>
       </x:c>
       <x:c r="B318" s="9" t="str">
-        <x:v>RP-SR5D2</x:v>
+        <x:v>RP-SR7A</x:v>
       </x:c>
       <x:c r="C318" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D318" s="9" t="n">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E318" s="10" t="b">
         <x:v>0</x:v>
@@ -7597,21 +7597,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G318" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="9" t="str">
-        <x:v>RP-SR6A</x:v>
+        <x:v>RP-SR7B</x:v>
       </x:c>
       <x:c r="B319" s="9" t="str">
-        <x:v>RP-SR6A</x:v>
+        <x:v>RP-SR7B</x:v>
       </x:c>
       <x:c r="C319" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D319" s="9" t="n">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E319" s="10" t="b">
         <x:v>0</x:v>
@@ -7625,16 +7625,16 @@
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="9" t="str">
-        <x:v>RP-SR6B</x:v>
+        <x:v>RP-SR7C</x:v>
       </x:c>
       <x:c r="B320" s="9" t="str">
-        <x:v>RP-SR6B</x:v>
+        <x:v>RP-SR7C</x:v>
       </x:c>
       <x:c r="C320" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D320" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E320" s="10" t="b">
         <x:v>0</x:v>
@@ -7648,16 +7648,16 @@
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="9" t="str">
-        <x:v>RP-SR6C</x:v>
+        <x:v>RP-SR7D</x:v>
       </x:c>
       <x:c r="B321" s="9" t="str">
-        <x:v>RP-SR6C</x:v>
+        <x:v>RP-SR7D</x:v>
       </x:c>
       <x:c r="C321" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D321" s="9" t="n">
-        <x:v>18</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E321" s="10" t="b">
         <x:v>0</x:v>
@@ -7671,16 +7671,16 @@
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="9" t="str">
-        <x:v>RP-SR6D</x:v>
+        <x:v>RP-SR7F</x:v>
       </x:c>
       <x:c r="B322" s="9" t="str">
-        <x:v>RP-SR6D</x:v>
+        <x:v>RP-SR7F</x:v>
       </x:c>
       <x:c r="C322" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D322" s="9" t="n">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E322" s="10" t="b">
         <x:v>0</x:v>
@@ -7694,16 +7694,16 @@
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="9" t="str">
-        <x:v>RP-SR6E</x:v>
+        <x:v>RP-SR7G</x:v>
       </x:c>
       <x:c r="B323" s="9" t="str">
-        <x:v>RP-SR6E</x:v>
+        <x:v>RP-SR7G</x:v>
       </x:c>
       <x:c r="C323" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D323" s="9" t="n">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E323" s="10" t="b">
         <x:v>0</x:v>
@@ -7717,16 +7717,16 @@
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="9" t="str">
-        <x:v>RP-SR6F</x:v>
+        <x:v>RP-SR8A</x:v>
       </x:c>
       <x:c r="B324" s="9" t="str">
-        <x:v>RP-SR6F</x:v>
+        <x:v>RP-SR8A</x:v>
       </x:c>
       <x:c r="C324" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D324" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E324" s="10" t="b">
         <x:v>0</x:v>
@@ -7735,15 +7735,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G324" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="9" t="str">
-        <x:v>RP-SR7A</x:v>
+        <x:v>RP-SR8B</x:v>
       </x:c>
       <x:c r="B325" s="9" t="str">
-        <x:v>RP-SR7A</x:v>
+        <x:v>RP-SR8B</x:v>
       </x:c>
       <x:c r="C325" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -7758,15 +7758,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G325" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="9" t="str">
-        <x:v>RP-SR7B</x:v>
+        <x:v>RP-SR8C</x:v>
       </x:c>
       <x:c r="B326" s="9" t="str">
-        <x:v>RP-SR7B</x:v>
+        <x:v>RP-SR8C</x:v>
       </x:c>
       <x:c r="C326" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -7786,16 +7786,16 @@
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="9" t="str">
-        <x:v>RP-SR7C</x:v>
+        <x:v>RP-SR9A</x:v>
       </x:c>
       <x:c r="B327" s="9" t="str">
-        <x:v>RP-SR7C</x:v>
+        <x:v>RP-SR9A</x:v>
       </x:c>
       <x:c r="C327" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D327" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E327" s="10" t="b">
         <x:v>0</x:v>
@@ -7809,16 +7809,16 @@
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="9" t="str">
-        <x:v>RP-SR7D</x:v>
+        <x:v>RP-SR9B</x:v>
       </x:c>
       <x:c r="B328" s="9" t="str">
-        <x:v>RP-SR7D</x:v>
+        <x:v>RP-SR9B</x:v>
       </x:c>
       <x:c r="C328" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D328" s="9" t="n">
-        <x:v>88</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E328" s="10" t="b">
         <x:v>0</x:v>
@@ -7832,16 +7832,16 @@
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="9" t="str">
-        <x:v>RP-SR7F</x:v>
+        <x:v>SP-LT4A</x:v>
       </x:c>
       <x:c r="B329" s="9" t="str">
-        <x:v>RP-SR7F</x:v>
+        <x:v>SP-LT4A</x:v>
       </x:c>
       <x:c r="C329" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D329" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E329" s="10" t="b">
         <x:v>0</x:v>
@@ -7855,16 +7855,16 @@
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="9" t="str">
-        <x:v>RP-SR7G</x:v>
+        <x:v>SP-LT4B</x:v>
       </x:c>
       <x:c r="B330" s="9" t="str">
-        <x:v>RP-SR7G</x:v>
+        <x:v>SP-LT4B</x:v>
       </x:c>
       <x:c r="C330" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D330" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E330" s="10" t="b">
         <x:v>0</x:v>
@@ -7878,16 +7878,16 @@
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="9" t="str">
-        <x:v>RP-SR8A</x:v>
+        <x:v>SP-LT5A</x:v>
       </x:c>
       <x:c r="B331" s="9" t="str">
-        <x:v>RP-SR8A</x:v>
+        <x:v>SP-LT5A</x:v>
       </x:c>
       <x:c r="C331" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D331" s="9" t="n">
-        <x:v>100</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E331" s="10" t="b">
         <x:v>0</x:v>
@@ -7896,21 +7896,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G331" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="9" t="str">
-        <x:v>RP-SR8B</x:v>
+        <x:v>SP-LT5B</x:v>
       </x:c>
       <x:c r="B332" s="9" t="str">
-        <x:v>RP-SR8B</x:v>
+        <x:v>SP-LT5B</x:v>
       </x:c>
       <x:c r="C332" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D332" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E332" s="10" t="b">
         <x:v>0</x:v>
@@ -7919,21 +7919,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G332" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="9" t="str">
-        <x:v>RP-SR8C</x:v>
+        <x:v>SP-LT6A</x:v>
       </x:c>
       <x:c r="B333" s="9" t="str">
-        <x:v>RP-SR8C</x:v>
+        <x:v>SP-LT6A</x:v>
       </x:c>
       <x:c r="C333" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D333" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E333" s="10" t="b">
         <x:v>0</x:v>
@@ -7947,16 +7947,16 @@
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="9" t="str">
-        <x:v>RP-SR9A</x:v>
+        <x:v>SP-LT6B</x:v>
       </x:c>
       <x:c r="B334" s="9" t="str">
-        <x:v>RP-SR9A</x:v>
+        <x:v>SP-LT6B</x:v>
       </x:c>
       <x:c r="C334" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D334" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E334" s="10" t="b">
         <x:v>0</x:v>
@@ -7970,16 +7970,16 @@
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="9" t="str">
-        <x:v>RP-SR9B</x:v>
+        <x:v>SP-LT6C</x:v>
       </x:c>
       <x:c r="B335" s="9" t="str">
-        <x:v>RP-SR9B</x:v>
+        <x:v>SP-LT6C</x:v>
       </x:c>
       <x:c r="C335" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D335" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E335" s="10" t="b">
         <x:v>0</x:v>
@@ -7993,16 +7993,16 @@
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="9" t="str">
-        <x:v>SP-LT4A</x:v>
+        <x:v>SP-LT6D</x:v>
       </x:c>
       <x:c r="B336" s="9" t="str">
-        <x:v>SP-LT4A</x:v>
+        <x:v>SP-LT6D</x:v>
       </x:c>
       <x:c r="C336" s="9" t="str">
         <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D336" s="9" t="n">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E336" s="10" t="b">
         <x:v>0</x:v>
@@ -8016,16 +8016,16 @@
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="9" t="str">
-        <x:v>SP-LT4B</x:v>
+        <x:v>SP-SR1A</x:v>
       </x:c>
       <x:c r="B337" s="9" t="str">
-        <x:v>SP-LT4B</x:v>
+        <x:v>SP-SR1A</x:v>
       </x:c>
       <x:c r="C337" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D337" s="9" t="n">
-        <x:v>36</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E337" s="10" t="b">
         <x:v>0</x:v>
@@ -8034,21 +8034,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G337" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="9" t="str">
-        <x:v>SP-LT5A</x:v>
+        <x:v>SP-SR1B</x:v>
       </x:c>
       <x:c r="B338" s="9" t="str">
-        <x:v>SP-LT5A</x:v>
+        <x:v>SP-SR1B</x:v>
       </x:c>
       <x:c r="C338" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D338" s="9" t="n">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E338" s="10" t="b">
         <x:v>0</x:v>
@@ -8057,21 +8057,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G338" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="9" t="str">
-        <x:v>SP-LT5B</x:v>
+        <x:v>SP-SR1C</x:v>
       </x:c>
       <x:c r="B339" s="9" t="str">
-        <x:v>SP-LT5B</x:v>
+        <x:v>SP-SR1C</x:v>
       </x:c>
       <x:c r="C339" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D339" s="9" t="n">
-        <x:v>37</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E339" s="10" t="b">
         <x:v>0</x:v>
@@ -8080,21 +8080,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G339" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="9" t="str">
-        <x:v>SP-LT6A</x:v>
+        <x:v>SP-SR2A</x:v>
       </x:c>
       <x:c r="B340" s="9" t="str">
-        <x:v>SP-LT6A</x:v>
+        <x:v>SP-SR2A</x:v>
       </x:c>
       <x:c r="C340" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D340" s="9" t="n">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E340" s="10" t="b">
         <x:v>0</x:v>
@@ -8103,21 +8103,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G340" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="9" t="str">
-        <x:v>SP-LT6B</x:v>
+        <x:v>SP-SR2B</x:v>
       </x:c>
       <x:c r="B341" s="9" t="str">
-        <x:v>SP-LT6B</x:v>
+        <x:v>SP-SR2B</x:v>
       </x:c>
       <x:c r="C341" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D341" s="9" t="n">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E341" s="10" t="b">
         <x:v>0</x:v>
@@ -8126,21 +8126,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G341" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="9" t="str">
-        <x:v>SP-LT6C</x:v>
+        <x:v>SP-SR2C</x:v>
       </x:c>
       <x:c r="B342" s="9" t="str">
-        <x:v>SP-LT6C</x:v>
+        <x:v>SP-SR2C</x:v>
       </x:c>
       <x:c r="C342" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D342" s="9" t="n">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E342" s="10" t="b">
         <x:v>0</x:v>
@@ -8149,21 +8149,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G342" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="9" t="str">
-        <x:v>SP-LT6D</x:v>
+        <x:v>SP-SR2D</x:v>
       </x:c>
       <x:c r="B343" s="9" t="str">
-        <x:v>SP-LT6D</x:v>
+        <x:v>SP-SR2D</x:v>
       </x:c>
       <x:c r="C343" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D343" s="9" t="n">
-        <x:v>41</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E343" s="10" t="b">
         <x:v>0</x:v>
@@ -8172,21 +8172,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G343" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="9" t="str">
-        <x:v>SP-SR1A</x:v>
+        <x:v>SP-SR2E</x:v>
       </x:c>
       <x:c r="B344" s="9" t="str">
-        <x:v>SP-SR1A</x:v>
+        <x:v>SP-SR2E</x:v>
       </x:c>
       <x:c r="C344" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D344" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E344" s="10" t="b">
         <x:v>0</x:v>
@@ -8200,16 +8200,16 @@
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="9" t="str">
-        <x:v>SP-SR1B</x:v>
+        <x:v>SP-SR2F</x:v>
       </x:c>
       <x:c r="B345" s="9" t="str">
-        <x:v>SP-SR1B</x:v>
+        <x:v>SP-SR2F</x:v>
       </x:c>
       <x:c r="C345" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D345" s="9" t="n">
-        <x:v>22</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E345" s="10" t="b">
         <x:v>0</x:v>
@@ -8223,16 +8223,16 @@
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="9" t="str">
-        <x:v>SP-SR1C</x:v>
+        <x:v>SP-SR2G</x:v>
       </x:c>
       <x:c r="B346" s="9" t="str">
-        <x:v>SP-SR1C</x:v>
+        <x:v>SP-SR2G</x:v>
       </x:c>
       <x:c r="C346" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D346" s="9" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E346" s="10" t="b">
         <x:v>0</x:v>
@@ -8246,16 +8246,16 @@
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="9" t="str">
-        <x:v>SP-SR2A</x:v>
+        <x:v>SP-SR2H</x:v>
       </x:c>
       <x:c r="B347" s="9" t="str">
-        <x:v>SP-SR2A</x:v>
+        <x:v>SP-SR2H</x:v>
       </x:c>
       <x:c r="C347" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D347" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E347" s="10" t="b">
         <x:v>0</x:v>
@@ -8269,16 +8269,16 @@
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="9" t="str">
-        <x:v>SP-SR2B</x:v>
+        <x:v>SP-SR3A</x:v>
       </x:c>
       <x:c r="B348" s="9" t="str">
-        <x:v>SP-SR2B</x:v>
+        <x:v>SP-SR3A</x:v>
       </x:c>
       <x:c r="C348" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D348" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E348" s="10" t="b">
         <x:v>0</x:v>
@@ -8292,10 +8292,10 @@
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="9" t="str">
-        <x:v>SP-SR2C</x:v>
+        <x:v>SP-SR3B</x:v>
       </x:c>
       <x:c r="B349" s="9" t="str">
-        <x:v>SP-SR2C</x:v>
+        <x:v>SP-SR3B</x:v>
       </x:c>
       <x:c r="C349" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -8315,10 +8315,10 @@
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="9" t="str">
-        <x:v>SP-SR2D</x:v>
+        <x:v>SP-SR3C</x:v>
       </x:c>
       <x:c r="B350" s="9" t="str">
-        <x:v>SP-SR2D</x:v>
+        <x:v>SP-SR3C</x:v>
       </x:c>
       <x:c r="C350" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -8338,10 +8338,10 @@
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="9" t="str">
-        <x:v>SP-SR2E</x:v>
+        <x:v>SP-SR3D</x:v>
       </x:c>
       <x:c r="B351" s="9" t="str">
-        <x:v>SP-SR2E</x:v>
+        <x:v>SP-SR3D</x:v>
       </x:c>
       <x:c r="C351" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -8361,16 +8361,16 @@
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="9" t="str">
-        <x:v>SP-SR2F</x:v>
+        <x:v>SP-SR3E</x:v>
       </x:c>
       <x:c r="B352" s="9" t="str">
-        <x:v>SP-SR2F</x:v>
+        <x:v>SP-SR3E</x:v>
       </x:c>
       <x:c r="C352" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D352" s="9" t="n">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E352" s="10" t="b">
         <x:v>0</x:v>
@@ -8384,16 +8384,16 @@
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="9" t="str">
-        <x:v>SP-SR2G</x:v>
+        <x:v>SP-SR3F</x:v>
       </x:c>
       <x:c r="B353" s="9" t="str">
-        <x:v>SP-SR2G</x:v>
+        <x:v>SP-SR3F</x:v>
       </x:c>
       <x:c r="C353" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D353" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E353" s="10" t="b">
         <x:v>0</x:v>
@@ -8407,16 +8407,16 @@
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="9" t="str">
-        <x:v>SP-SR2H</x:v>
+        <x:v>SP-SR3G</x:v>
       </x:c>
       <x:c r="B354" s="9" t="str">
-        <x:v>SP-SR2H</x:v>
+        <x:v>SP-SR3G</x:v>
       </x:c>
       <x:c r="C354" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D354" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E354" s="10" t="b">
         <x:v>0</x:v>
@@ -8430,16 +8430,16 @@
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="9" t="str">
-        <x:v>SP-SR3A</x:v>
+        <x:v>SP-SR3H</x:v>
       </x:c>
       <x:c r="B355" s="9" t="str">
-        <x:v>SP-SR3A</x:v>
+        <x:v>SP-SR3H</x:v>
       </x:c>
       <x:c r="C355" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D355" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E355" s="10" t="b">
         <x:v>0</x:v>
@@ -8453,10 +8453,10 @@
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="9" t="str">
-        <x:v>SP-SR3B</x:v>
+        <x:v>SP-SR3J</x:v>
       </x:c>
       <x:c r="B356" s="9" t="str">
-        <x:v>SP-SR3B</x:v>
+        <x:v>SP-SR3J</x:v>
       </x:c>
       <x:c r="C356" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -8476,16 +8476,16 @@
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="9" t="str">
-        <x:v>SP-SR3C</x:v>
+        <x:v>SP-SR3K</x:v>
       </x:c>
       <x:c r="B357" s="9" t="str">
-        <x:v>SP-SR3C</x:v>
+        <x:v>SP-SR3K</x:v>
       </x:c>
       <x:c r="C357" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D357" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E357" s="10" t="b">
         <x:v>0</x:v>
@@ -8499,16 +8499,16 @@
     </x:row>
     <x:row r="358">
       <x:c r="A358" s="9" t="str">
-        <x:v>SP-SR3D</x:v>
+        <x:v>SP-SR4A</x:v>
       </x:c>
       <x:c r="B358" s="9" t="str">
-        <x:v>SP-SR3D</x:v>
+        <x:v>SP-SR4A</x:v>
       </x:c>
       <x:c r="C358" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D358" s="9" t="n">
-        <x:v>80</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E358" s="10" t="b">
         <x:v>0</x:v>
@@ -8522,16 +8522,16 @@
     </x:row>
     <x:row r="359">
       <x:c r="A359" s="9" t="str">
-        <x:v>SP-SR3E</x:v>
+        <x:v>SP-SR4B</x:v>
       </x:c>
       <x:c r="B359" s="9" t="str">
-        <x:v>SP-SR3E</x:v>
+        <x:v>SP-SR4B</x:v>
       </x:c>
       <x:c r="C359" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D359" s="9" t="n">
-        <x:v>75</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E359" s="10" t="b">
         <x:v>0</x:v>
@@ -8545,16 +8545,16 @@
     </x:row>
     <x:row r="360">
       <x:c r="A360" s="9" t="str">
-        <x:v>SP-SR3F</x:v>
+        <x:v>SP-SR4C</x:v>
       </x:c>
       <x:c r="B360" s="9" t="str">
-        <x:v>SP-SR3F</x:v>
+        <x:v>SP-SR4C</x:v>
       </x:c>
       <x:c r="C360" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D360" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E360" s="10" t="b">
         <x:v>0</x:v>
@@ -8568,16 +8568,16 @@
     </x:row>
     <x:row r="361">
       <x:c r="A361" s="9" t="str">
-        <x:v>SP-SR3G</x:v>
+        <x:v>SP-SR4D</x:v>
       </x:c>
       <x:c r="B361" s="9" t="str">
-        <x:v>SP-SR3G</x:v>
+        <x:v>SP-SR4D</x:v>
       </x:c>
       <x:c r="C361" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D361" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E361" s="10" t="b">
         <x:v>0</x:v>
@@ -8591,16 +8591,16 @@
     </x:row>
     <x:row r="362">
       <x:c r="A362" s="9" t="str">
-        <x:v>SP-SR3H</x:v>
+        <x:v>SP-SR4E</x:v>
       </x:c>
       <x:c r="B362" s="9" t="str">
-        <x:v>SP-SR3H</x:v>
+        <x:v>SP-SR4E</x:v>
       </x:c>
       <x:c r="C362" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D362" s="9" t="n">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E362" s="10" t="b">
         <x:v>0</x:v>
@@ -8614,16 +8614,16 @@
     </x:row>
     <x:row r="363">
       <x:c r="A363" s="9" t="str">
-        <x:v>SP-SR3J</x:v>
+        <x:v>SP-SR4F</x:v>
       </x:c>
       <x:c r="B363" s="9" t="str">
-        <x:v>SP-SR3J</x:v>
+        <x:v>SP-SR4F</x:v>
       </x:c>
       <x:c r="C363" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D363" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E363" s="10" t="b">
         <x:v>0</x:v>
@@ -8632,21 +8632,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G363" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="9" t="str">
-        <x:v>SP-SR3K</x:v>
+        <x:v>SP-SR4G</x:v>
       </x:c>
       <x:c r="B364" s="9" t="str">
-        <x:v>SP-SR3K</x:v>
+        <x:v>SP-SR4G</x:v>
       </x:c>
       <x:c r="C364" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D364" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E364" s="10" t="b">
         <x:v>0</x:v>
@@ -8655,21 +8655,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G364" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="365">
       <x:c r="A365" s="9" t="str">
-        <x:v>SP-SR4A</x:v>
+        <x:v>SP-SR4H</x:v>
       </x:c>
       <x:c r="B365" s="9" t="str">
-        <x:v>SP-SR4A</x:v>
+        <x:v>SP-SR4H</x:v>
       </x:c>
       <x:c r="C365" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D365" s="9" t="n">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E365" s="10" t="b">
         <x:v>0</x:v>
@@ -8683,16 +8683,16 @@
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="9" t="str">
-        <x:v>SP-SR4B</x:v>
+        <x:v>SP-SR4J</x:v>
       </x:c>
       <x:c r="B366" s="9" t="str">
-        <x:v>SP-SR4B</x:v>
+        <x:v>SP-SR4J</x:v>
       </x:c>
       <x:c r="C366" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D366" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E366" s="10" t="b">
         <x:v>0</x:v>
@@ -8706,10 +8706,10 @@
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="9" t="str">
-        <x:v>SP-SR4C</x:v>
+        <x:v>SP-SR5A</x:v>
       </x:c>
       <x:c r="B367" s="9" t="str">
-        <x:v>SP-SR4C</x:v>
+        <x:v>*SP-SR5A</x:v>
       </x:c>
       <x:c r="C367" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -8729,10 +8729,10 @@
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="9" t="str">
-        <x:v>SP-SR4D</x:v>
+        <x:v>SP-SR5B</x:v>
       </x:c>
       <x:c r="B368" s="9" t="str">
-        <x:v>SP-SR4D</x:v>
+        <x:v>*SP-SR5B</x:v>
       </x:c>
       <x:c r="C368" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -8752,16 +8752,16 @@
     </x:row>
     <x:row r="369">
       <x:c r="A369" s="9" t="str">
-        <x:v>SP-SR4E</x:v>
+        <x:v>SP-SR5C</x:v>
       </x:c>
       <x:c r="B369" s="9" t="str">
-        <x:v>SP-SR4E</x:v>
+        <x:v>SP-SR5C</x:v>
       </x:c>
       <x:c r="C369" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D369" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E369" s="10" t="b">
         <x:v>0</x:v>
@@ -8770,15 +8770,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G369" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="370">
       <x:c r="A370" s="9" t="str">
-        <x:v>SP-SR4F</x:v>
+        <x:v>SP-SR5D</x:v>
       </x:c>
       <x:c r="B370" s="9" t="str">
-        <x:v>SP-SR4F</x:v>
+        <x:v>SP-SR5D</x:v>
       </x:c>
       <x:c r="C370" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -8798,16 +8798,16 @@
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="9" t="str">
-        <x:v>SP-SR4G</x:v>
+        <x:v>SP-SR5E</x:v>
       </x:c>
       <x:c r="B371" s="9" t="str">
-        <x:v>SP-SR4G</x:v>
+        <x:v>SP-SR5E</x:v>
       </x:c>
       <x:c r="C371" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D371" s="9" t="n">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E371" s="10" t="b">
         <x:v>0</x:v>
@@ -8821,16 +8821,16 @@
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="9" t="str">
-        <x:v>SP-SR4H</x:v>
+        <x:v>SP-SR5F</x:v>
       </x:c>
       <x:c r="B372" s="9" t="str">
-        <x:v>SP-SR4H</x:v>
+        <x:v>SP-SR5F</x:v>
       </x:c>
       <x:c r="C372" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D372" s="9" t="n">
-        <x:v>75</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E372" s="10" t="b">
         <x:v>0</x:v>
@@ -8844,16 +8844,16 @@
     </x:row>
     <x:row r="373">
       <x:c r="A373" s="9" t="str">
-        <x:v>SP-SR4J</x:v>
+        <x:v>SP-SR5G</x:v>
       </x:c>
       <x:c r="B373" s="9" t="str">
-        <x:v>SP-SR4J</x:v>
+        <x:v>*SP-SR5G</x:v>
       </x:c>
       <x:c r="C373" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D373" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E373" s="10" t="b">
         <x:v>0</x:v>
@@ -8867,16 +8867,16 @@
     </x:row>
     <x:row r="374">
       <x:c r="A374" s="9" t="str">
-        <x:v>SP-SR5C</x:v>
+        <x:v>SP-SR5H</x:v>
       </x:c>
       <x:c r="B374" s="9" t="str">
-        <x:v>SP-SR5C</x:v>
+        <x:v>SP-SR5H</x:v>
       </x:c>
       <x:c r="C374" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D374" s="9" t="n">
-        <x:v>36</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E374" s="10" t="b">
         <x:v>0</x:v>
@@ -8885,21 +8885,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G374" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="375">
       <x:c r="A375" s="9" t="str">
-        <x:v>SP-SR5D</x:v>
+        <x:v>SP-SR5J</x:v>
       </x:c>
       <x:c r="B375" s="9" t="str">
-        <x:v>SP-SR5D</x:v>
+        <x:v>SP-SR5J</x:v>
       </x:c>
       <x:c r="C375" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D375" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E375" s="10" t="b">
         <x:v>0</x:v>
@@ -8908,21 +8908,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G375" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="9" t="str">
-        <x:v>SP-SR5E</x:v>
+        <x:v>SP-SR5K</x:v>
       </x:c>
       <x:c r="B376" s="9" t="str">
-        <x:v>SP-SR5E</x:v>
+        <x:v>*SP-SR5K</x:v>
       </x:c>
       <x:c r="C376" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D376" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E376" s="10" t="b">
         <x:v>0</x:v>
@@ -8931,21 +8931,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G376" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="9" t="str">
-        <x:v>SP-SR5F</x:v>
+        <x:v>SP-SR6A</x:v>
       </x:c>
       <x:c r="B377" s="9" t="str">
-        <x:v>SP-SR5F</x:v>
+        <x:v>SP-SR6A</x:v>
       </x:c>
       <x:c r="C377" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D377" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E377" s="10" t="b">
         <x:v>0</x:v>
@@ -8954,15 +8954,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G377" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="9" t="str">
-        <x:v>SP-SR5H</x:v>
+        <x:v>SP-SR6B</x:v>
       </x:c>
       <x:c r="B378" s="9" t="str">
-        <x:v>SP-SR5H</x:v>
+        <x:v>SP-SR6B</x:v>
       </x:c>
       <x:c r="C378" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -8982,16 +8982,16 @@
     </x:row>
     <x:row r="379">
       <x:c r="A379" s="9" t="str">
-        <x:v>SP-SR5J</x:v>
+        <x:v>SP-SR6C</x:v>
       </x:c>
       <x:c r="B379" s="9" t="str">
-        <x:v>SP-SR5J</x:v>
+        <x:v>SP-SR6C</x:v>
       </x:c>
       <x:c r="C379" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D379" s="9" t="n">
-        <x:v>75</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E379" s="10" t="b">
         <x:v>0</x:v>
@@ -9005,16 +9005,16 @@
     </x:row>
     <x:row r="380">
       <x:c r="A380" s="9" t="str">
-        <x:v>SP-SR6A</x:v>
+        <x:v>SP-SR6D</x:v>
       </x:c>
       <x:c r="B380" s="9" t="str">
-        <x:v>SP-SR6A</x:v>
+        <x:v>SP-SR6D Seminar Room</x:v>
       </x:c>
       <x:c r="C380" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D380" s="9" t="n">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E380" s="10" t="b">
         <x:v>0</x:v>
@@ -9023,21 +9023,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G380" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="381">
       <x:c r="A381" s="9" t="str">
-        <x:v>SP-SR6B</x:v>
+        <x:v>SP-SR6E</x:v>
       </x:c>
       <x:c r="B381" s="9" t="str">
-        <x:v>SP-SR6B</x:v>
+        <x:v>SP-SR6E Seminar Room</x:v>
       </x:c>
       <x:c r="C381" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D381" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E381" s="10" t="b">
         <x:v>0</x:v>
@@ -9051,16 +9051,16 @@
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="9" t="str">
-        <x:v>SP-SR6C</x:v>
+        <x:v>SP-SR6F</x:v>
       </x:c>
       <x:c r="B382" s="9" t="str">
-        <x:v>SP-SR6C</x:v>
+        <x:v>SP-SR6F</x:v>
       </x:c>
       <x:c r="C382" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D382" s="9" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E382" s="10" t="b">
         <x:v>0</x:v>
@@ -9074,16 +9074,16 @@
     </x:row>
     <x:row r="383">
       <x:c r="A383" s="9" t="str">
-        <x:v>SP-SR6D Seminar Room</x:v>
+        <x:v>TP-LT1A</x:v>
       </x:c>
       <x:c r="B383" s="9" t="str">
-        <x:v>SP-SR6D</x:v>
+        <x:v>TP-LT1A</x:v>
       </x:c>
       <x:c r="C383" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D383" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E383" s="10" t="b">
         <x:v>0</x:v>
@@ -9092,18 +9092,18 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G383" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="384">
       <x:c r="A384" s="9" t="str">
-        <x:v>SP-SR6E Seminar Room</x:v>
+        <x:v>TP-LT1B</x:v>
       </x:c>
       <x:c r="B384" s="9" t="str">
-        <x:v>SP-SR6E</x:v>
+        <x:v>TP-LT1B</x:v>
       </x:c>
       <x:c r="C384" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D384" s="9" t="n">
         <x:v>25</x:v>
@@ -9115,21 +9115,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G384" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="9" t="str">
-        <x:v>SP-SR6F</x:v>
+        <x:v>TP-LT2A</x:v>
       </x:c>
       <x:c r="B385" s="9" t="str">
-        <x:v>SP-SR6F</x:v>
+        <x:v>TP-LT2A</x:v>
       </x:c>
       <x:c r="C385" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Lecture Theatre</x:v>
       </x:c>
       <x:c r="D385" s="9" t="n">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E385" s="10" t="b">
         <x:v>0</x:v>
@@ -9138,15 +9138,15 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G385" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="386">
       <x:c r="A386" s="9" t="str">
-        <x:v>TP-LT1A</x:v>
+        <x:v>TP-LT5A</x:v>
       </x:c>
       <x:c r="B386" s="9" t="str">
-        <x:v>TP-LT1A</x:v>
+        <x:v>TP-LT5A</x:v>
       </x:c>
       <x:c r="C386" s="9" t="str">
         <x:v>Lecture Theatre</x:v>
@@ -9166,16 +9166,16 @@
     </x:row>
     <x:row r="387">
       <x:c r="A387" s="9" t="str">
-        <x:v>TP-LT1B</x:v>
+        <x:v>TP-SR1A</x:v>
       </x:c>
       <x:c r="B387" s="9" t="str">
-        <x:v>TP-LT1B</x:v>
+        <x:v>TP-SR1A</x:v>
       </x:c>
       <x:c r="C387" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D387" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E387" s="10" t="b">
         <x:v>0</x:v>
@@ -9189,16 +9189,16 @@
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="9" t="str">
-        <x:v>TP-LT2A</x:v>
+        <x:v>TP-SR2A</x:v>
       </x:c>
       <x:c r="B388" s="9" t="str">
-        <x:v>TP-LT2A</x:v>
+        <x:v>TP-SR2A</x:v>
       </x:c>
       <x:c r="C388" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D388" s="9" t="n">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E388" s="10" t="b">
         <x:v>0</x:v>
@@ -9212,16 +9212,16 @@
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="9" t="str">
-        <x:v>TP-LT5A</x:v>
+        <x:v>TP-SR2B</x:v>
       </x:c>
       <x:c r="B389" s="9" t="str">
-        <x:v>TP-LT5A</x:v>
+        <x:v>TP-SR2B</x:v>
       </x:c>
       <x:c r="C389" s="9" t="str">
-        <x:v>Lecture Theatre</x:v>
+        <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D389" s="9" t="n">
-        <x:v>49</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E389" s="10" t="b">
         <x:v>0</x:v>
@@ -9235,16 +9235,16 @@
     </x:row>
     <x:row r="390">
       <x:c r="A390" s="9" t="str">
-        <x:v>TP-SR1A</x:v>
+        <x:v>TP-SR2C</x:v>
       </x:c>
       <x:c r="B390" s="9" t="str">
-        <x:v>TP-SR1A</x:v>
+        <x:v>TP-SR2C</x:v>
       </x:c>
       <x:c r="C390" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D390" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E390" s="10" t="b">
         <x:v>0</x:v>
@@ -9258,16 +9258,16 @@
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="9" t="str">
-        <x:v>TP-SR2A</x:v>
+        <x:v>TP-SR2D</x:v>
       </x:c>
       <x:c r="B391" s="9" t="str">
-        <x:v>TP-SR2A</x:v>
+        <x:v>TP-SR2D</x:v>
       </x:c>
       <x:c r="C391" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D391" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E391" s="10" t="b">
         <x:v>0</x:v>
@@ -9281,10 +9281,10 @@
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="9" t="str">
-        <x:v>TP-SR2B</x:v>
+        <x:v>TP-SR2E</x:v>
       </x:c>
       <x:c r="B392" s="9" t="str">
-        <x:v>TP-SR2B</x:v>
+        <x:v>TP-SR2E</x:v>
       </x:c>
       <x:c r="C392" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -9304,16 +9304,16 @@
     </x:row>
     <x:row r="393">
       <x:c r="A393" s="9" t="str">
-        <x:v>TP-SR2C</x:v>
+        <x:v>TP-SR3A</x:v>
       </x:c>
       <x:c r="B393" s="9" t="str">
-        <x:v>TP-SR2C</x:v>
+        <x:v>TP-SR3A</x:v>
       </x:c>
       <x:c r="C393" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D393" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E393" s="10" t="b">
         <x:v>0</x:v>
@@ -9322,21 +9322,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G393" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="9" t="str">
-        <x:v>TP-SR2D</x:v>
+        <x:v>TP-SR3B</x:v>
       </x:c>
       <x:c r="B394" s="9" t="str">
-        <x:v>TP-SR2D</x:v>
+        <x:v>TP-SR3B</x:v>
       </x:c>
       <x:c r="C394" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D394" s="9" t="n">
-        <x:v>22</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E394" s="10" t="b">
         <x:v>0</x:v>
@@ -9345,21 +9345,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G394" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="395">
       <x:c r="A395" s="9" t="str">
-        <x:v>TP-SR2E</x:v>
+        <x:v>TP-SR3C</x:v>
       </x:c>
       <x:c r="B395" s="9" t="str">
-        <x:v>TP-SR2E</x:v>
+        <x:v>TP-SR3C</x:v>
       </x:c>
       <x:c r="C395" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D395" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E395" s="10" t="b">
         <x:v>0</x:v>
@@ -9373,16 +9373,16 @@
     </x:row>
     <x:row r="396">
       <x:c r="A396" s="9" t="str">
-        <x:v>TP-SR3A</x:v>
+        <x:v>TP-SR3D</x:v>
       </x:c>
       <x:c r="B396" s="9" t="str">
-        <x:v>TP-SR3A</x:v>
+        <x:v>TP-SR3D</x:v>
       </x:c>
       <x:c r="C396" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D396" s="9" t="n">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E396" s="10" t="b">
         <x:v>0</x:v>
@@ -9391,21 +9391,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G396" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="397">
       <x:c r="A397" s="9" t="str">
-        <x:v>TP-SR3B</x:v>
+        <x:v>TP-SR3E</x:v>
       </x:c>
       <x:c r="B397" s="9" t="str">
-        <x:v>TP-SR3B</x:v>
+        <x:v>TP-SR3E</x:v>
       </x:c>
       <x:c r="C397" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D397" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E397" s="10" t="b">
         <x:v>0</x:v>
@@ -9414,21 +9414,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G397" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="9" t="str">
-        <x:v>TP-SR3C</x:v>
+        <x:v>TP-SR3F</x:v>
       </x:c>
       <x:c r="B398" s="9" t="str">
-        <x:v>TP-SR3C</x:v>
+        <x:v>*TP-SR3F</x:v>
       </x:c>
       <x:c r="C398" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D398" s="9" t="n">
-        <x:v>22</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E398" s="10" t="b">
         <x:v>0</x:v>
@@ -9437,21 +9437,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G398" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="399">
       <x:c r="A399" s="9" t="str">
-        <x:v>TP-SR3D</x:v>
+        <x:v>TP-SR3G</x:v>
       </x:c>
       <x:c r="B399" s="9" t="str">
-        <x:v>TP-SR3D</x:v>
+        <x:v>*TP-SR3G</x:v>
       </x:c>
       <x:c r="C399" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D399" s="9" t="n">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E399" s="10" t="b">
         <x:v>0</x:v>
@@ -9460,21 +9460,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G399" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="9" t="str">
-        <x:v>TP-SR3E</x:v>
+        <x:v>TP-SR3H</x:v>
       </x:c>
       <x:c r="B400" s="9" t="str">
-        <x:v>TP-SR3E</x:v>
+        <x:v>TP-SR3H</x:v>
       </x:c>
       <x:c r="C400" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D400" s="9" t="n">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E400" s="10" t="b">
         <x:v>0</x:v>
@@ -9483,21 +9483,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G400" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="9" t="str">
-        <x:v>TP-SR3H</x:v>
+        <x:v>TP-SR4A</x:v>
       </x:c>
       <x:c r="B401" s="9" t="str">
-        <x:v>TP-SR3H</x:v>
+        <x:v>TP-SR4A</x:v>
       </x:c>
       <x:c r="C401" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D401" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E401" s="10" t="b">
         <x:v>0</x:v>
@@ -9511,16 +9511,16 @@
     </x:row>
     <x:row r="402">
       <x:c r="A402" s="9" t="str">
-        <x:v>TP-SR4A</x:v>
+        <x:v>TP-SR4B</x:v>
       </x:c>
       <x:c r="B402" s="9" t="str">
-        <x:v>TP-SR4A</x:v>
+        <x:v>TP-SR4B</x:v>
       </x:c>
       <x:c r="C402" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D402" s="9" t="n">
-        <x:v>113</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E402" s="10" t="b">
         <x:v>0</x:v>
@@ -9534,10 +9534,10 @@
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="9" t="str">
-        <x:v>TP-SR4B</x:v>
+        <x:v>TP-SR4C</x:v>
       </x:c>
       <x:c r="B403" s="9" t="str">
-        <x:v>TP-SR4B</x:v>
+        <x:v>TP-SR4C</x:v>
       </x:c>
       <x:c r="C403" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -9557,16 +9557,16 @@
     </x:row>
     <x:row r="404">
       <x:c r="A404" s="9" t="str">
-        <x:v>TP-SR4C</x:v>
+        <x:v>TP-SR4D</x:v>
       </x:c>
       <x:c r="B404" s="9" t="str">
-        <x:v>TP-SR4C</x:v>
+        <x:v>TP-SR4D</x:v>
       </x:c>
       <x:c r="C404" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D404" s="9" t="n">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E404" s="10" t="b">
         <x:v>0</x:v>
@@ -9580,10 +9580,10 @@
     </x:row>
     <x:row r="405">
       <x:c r="A405" s="9" t="str">
-        <x:v>TP-SR4D</x:v>
+        <x:v>TP-SR4E</x:v>
       </x:c>
       <x:c r="B405" s="9" t="str">
-        <x:v>TP-SR4D</x:v>
+        <x:v>TP-SR4E</x:v>
       </x:c>
       <x:c r="C405" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -9603,10 +9603,10 @@
     </x:row>
     <x:row r="406">
       <x:c r="A406" s="9" t="str">
-        <x:v>TP-SR4E</x:v>
+        <x:v>TP-SR4F</x:v>
       </x:c>
       <x:c r="B406" s="9" t="str">
-        <x:v>TP-SR4E</x:v>
+        <x:v>TP-SR4F</x:v>
       </x:c>
       <x:c r="C406" s="9" t="str">
         <x:v>Seminar Room</x:v>
@@ -9626,16 +9626,16 @@
     </x:row>
     <x:row r="407">
       <x:c r="A407" s="9" t="str">
-        <x:v>TP-SR4F</x:v>
+        <x:v>TP-SR5A</x:v>
       </x:c>
       <x:c r="B407" s="9" t="str">
-        <x:v>TP-SR4F</x:v>
+        <x:v>TP-SR5A</x:v>
       </x:c>
       <x:c r="C407" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D407" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E407" s="10" t="b">
         <x:v>0</x:v>
@@ -9644,21 +9644,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G407" s="10" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="408">
       <x:c r="A408" s="9" t="str">
-        <x:v>TP-SR5A</x:v>
+        <x:v>TP-SR5B</x:v>
       </x:c>
       <x:c r="B408" s="9" t="str">
-        <x:v>TP-SR5A</x:v>
+        <x:v>TP-SR5B</x:v>
       </x:c>
       <x:c r="C408" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D408" s="9" t="n">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E408" s="10" t="b">
         <x:v>0</x:v>
@@ -9672,16 +9672,16 @@
     </x:row>
     <x:row r="409">
       <x:c r="A409" s="9" t="str">
-        <x:v>TP-SR5B</x:v>
+        <x:v>TP-SR5C</x:v>
       </x:c>
       <x:c r="B409" s="9" t="str">
-        <x:v>TP-SR5B</x:v>
+        <x:v>TP-SR5C</x:v>
       </x:c>
       <x:c r="C409" s="9" t="str">
         <x:v>Seminar Room</x:v>
       </x:c>
       <x:c r="D409" s="9" t="n">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E409" s="10" t="b">
         <x:v>0</x:v>
@@ -9690,21 +9690,21 @@
         <x:v>Physical</x:v>
       </x:c>
       <x:c r="G409" s="10" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="410">
       <x:c r="A410" s="9" t="str">
-        <x:v>TP-SR5C</x:v>
+        <x:v>Temp Venue001</x:v>
       </x:c>
       <x:c r="B410" s="9" t="str">
-        <x:v>TP-SR5C</x:v>
+        <x:v>*Temp Venue</x:v>
       </x:c>
       <x:c r="C410" s="9" t="str">
-        <x:v>Seminar Room</x:v>
+        <x:v>Teaching Facility</x:v>
       </x:c>
       <x:c r="D410" s="9" t="n">
-        <x:v>50</x:v>
+        <x:v>999</x:v>
       </x:c>
       <x:c r="E410" s="10" t="b">
         <x:v>0</x:v>

--- a/outputs/raw_data_cleaning/cleaned_raw_data_combined.xlsx
+++ b/outputs/raw_data_cleaning/cleaned_raw_data_combined.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rooms" sheetId="1" r:id="Rbc566847ba6b4980"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff" sheetId="2" r:id="R6ecdad78b7ad4036"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="3" r:id="R64ba38575a0949c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="4" r:id="Re584f4e2d09841ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Common Modules" sheetId="5" r:id="Re2e29e84f45a4733"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Common Module Map" sheetId="6" r:id="Red410997f5b54a2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded Rows" sheetId="7" r:id="Rdab94ed7111a4053"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleanup Notes" sheetId="8" r:id="R5d6cb2ba38224e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rooms" sheetId="1" r:id="Rbf3e0eed4b004148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff" sheetId="2" r:id="R2566c9e93e9e49ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="3" r:id="R954e1c1af3f146cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="4" r:id="Re64490349ba743e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Common Modules" sheetId="5" r:id="Ra43a181d39534e4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Common Module Map" sheetId="6" r:id="R84a0e07b402f402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded Rows" sheetId="7" r:id="Reeb13393d39045f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleanup Notes" sheetId="8" r:id="R400793ea3d5b428f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -186,12 +186,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
@@ -41626,7 +41672,7 @@
   <x:cols>
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="33.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -41637,7 +41683,7 @@
         <x:v>name</x:v>
       </x:c>
       <x:c r="C1" s="4" t="str">
-        <x:v>cluster</x:v>
+        <x:v>years</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -41647,8 +41693,8 @@
       <x:c r="B2" s="9" t="str">
         <x:v>AAI</x:v>
       </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C2" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -41658,8 +41704,8 @@
       <x:c r="B3" s="9" t="str">
         <x:v>ACC</x:v>
       </x:c>
-      <x:c r="C3" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C3" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -41669,8 +41715,8 @@
       <x:c r="B4" s="9" t="str">
         <x:v>ASE</x:v>
       </x:c>
-      <x:c r="C4" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C4" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -41680,8 +41726,8 @@
       <x:c r="B5" s="9" t="str">
         <x:v>ATM</x:v>
       </x:c>
-      <x:c r="C5" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C5" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -41691,8 +41737,8 @@
       <x:c r="B6" s="9" t="str">
         <x:v>BAC</x:v>
       </x:c>
-      <x:c r="C6" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C6" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -41702,9 +41748,7 @@
       <x:c r="B7" s="9" t="str">
         <x:v>BCD</x:v>
       </x:c>
-      <x:c r="C7" s="9" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C7" s="9"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="9" t="str">
@@ -41713,8 +41757,8 @@
       <x:c r="B8" s="9" t="str">
         <x:v>BICT</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C8" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -41724,9 +41768,7 @@
       <x:c r="B9" s="9" t="str">
         <x:v>CBE</x:v>
       </x:c>
-      <x:c r="C9" s="9" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C9" s="9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="9" t="str">
@@ -41735,8 +41777,8 @@
       <x:c r="B10" s="9" t="str">
         <x:v>CDM</x:v>
       </x:c>
-      <x:c r="C10" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C10" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -41746,8 +41788,8 @@
       <x:c r="B11" s="9" t="str">
         <x:v>CEG</x:v>
       </x:c>
-      <x:c r="C11" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C11" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -41757,9 +41799,7 @@
       <x:c r="B12" s="9" t="str">
         <x:v>CLASIC</x:v>
       </x:c>
-      <x:c r="C12" s="9" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C12" s="9"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9" t="str">
@@ -41768,9 +41808,7 @@
       <x:c r="B13" s="9" t="str">
         <x:v>CPC</x:v>
       </x:c>
-      <x:c r="C13" s="9" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C13" s="9"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9" t="str">
@@ -41779,8 +41817,8 @@
       <x:c r="B14" s="9" t="str">
         <x:v>CVE</x:v>
       </x:c>
-      <x:c r="C14" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C14" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -41790,8 +41828,8 @@
       <x:c r="B15" s="9" t="str">
         <x:v>DSC</x:v>
       </x:c>
-      <x:c r="C15" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C15" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -41801,8 +41839,8 @@
       <x:c r="B16" s="9" t="str">
         <x:v>EDE</x:v>
       </x:c>
-      <x:c r="C16" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C16" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -41812,8 +41850,8 @@
       <x:c r="B17" s="9" t="str">
         <x:v>EEE</x:v>
       </x:c>
-      <x:c r="C17" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C17" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -41823,9 +41861,7 @@
       <x:c r="B18" s="9" t="str">
         <x:v>ENG</x:v>
       </x:c>
-      <x:c r="C18" s="9" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C18" s="9"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="9" t="str">
@@ -41834,8 +41870,8 @@
       <x:c r="B19" s="9" t="str">
         <x:v>EPE</x:v>
       </x:c>
-      <x:c r="C19" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C19" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -41845,8 +41881,8 @@
       <x:c r="B20" s="9" t="str">
         <x:v>ESE</x:v>
       </x:c>
-      <x:c r="C20" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C20" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -41856,9 +41892,7 @@
       <x:c r="B21" s="9" t="str">
         <x:v>FCB</x:v>
       </x:c>
-      <x:c r="C21" s="9" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C21" s="9"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="9" t="str">
@@ -41867,8 +41901,8 @@
       <x:c r="B22" s="9" t="str">
         <x:v>FDT</x:v>
       </x:c>
-      <x:c r="C22" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C22" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -41878,9 +41912,7 @@
       <x:c r="B23" s="9" t="str">
         <x:v>HSS</x:v>
       </x:c>
-      <x:c r="C23" s="9" t="str">
-        <x:v>Module host key</x:v>
-      </x:c>
+      <x:c r="C23" s="9"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="9" t="str">
@@ -41889,8 +41921,8 @@
       <x:c r="B24" s="9" t="str">
         <x:v>HTM</x:v>
       </x:c>
-      <x:c r="C24" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C24" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -41900,8 +41932,8 @@
       <x:c r="B25" s="9" t="str">
         <x:v>ICT</x:v>
       </x:c>
-      <x:c r="C25" s="9" t="str">
-        <x:v>Common Modules, Module host key</x:v>
+      <x:c r="C25" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -41911,9 +41943,7 @@
       <x:c r="B26" s="9" t="str">
         <x:v>IS</x:v>
       </x:c>
-      <x:c r="C26" s="9" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C26" s="9"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="9" t="str">
@@ -41922,8 +41952,8 @@
       <x:c r="B27" s="9" t="str">
         <x:v>MDME</x:v>
       </x:c>
-      <x:c r="C27" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C27" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -41933,8 +41963,8 @@
       <x:c r="B28" s="9" t="str">
         <x:v>MEC</x:v>
       </x:c>
-      <x:c r="C28" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C28" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -41944,8 +41974,8 @@
       <x:c r="B29" s="9" t="str">
         <x:v>METS</x:v>
       </x:c>
-      <x:c r="C29" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C29" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -41955,8 +41985,8 @@
       <x:c r="B30" s="9" t="str">
         <x:v>NAME</x:v>
       </x:c>
-      <x:c r="C30" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C30" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -41966,8 +41996,8 @@
       <x:c r="B31" s="9" t="str">
         <x:v>NUR</x:v>
       </x:c>
-      <x:c r="C31" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C31" s="9" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -41977,9 +42007,7 @@
       <x:c r="B32" s="9" t="str">
         <x:v>POST</x:v>
       </x:c>
-      <x:c r="C32" s="9" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C32" s="9"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="9" t="str">
@@ -41988,9 +42016,7 @@
       <x:c r="B33" s="9" t="str">
         <x:v>PRE</x:v>
       </x:c>
-      <x:c r="C33" s="9" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C33" s="9"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="9" t="str">
@@ -41999,8 +42025,8 @@
       <x:c r="B34" s="9" t="str">
         <x:v>RSE</x:v>
       </x:c>
-      <x:c r="C34" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C34" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -42010,8 +42036,8 @@
       <x:c r="B35" s="9" t="str">
         <x:v>RTY</x:v>
       </x:c>
-      <x:c r="C35" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C35" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -42021,8 +42047,8 @@
       <x:c r="B36" s="9" t="str">
         <x:v>SBE</x:v>
       </x:c>
-      <x:c r="C36" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C36" s="9" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -42032,9 +42058,7 @@
       <x:c r="B37" s="9" t="str">
         <x:v>SE</x:v>
       </x:c>
-      <x:c r="C37" s="9" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C37" s="9"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="9" t="str">
@@ -42043,8 +42067,8 @@
       <x:c r="B38" s="9" t="str">
         <x:v>SLT</x:v>
       </x:c>
-      <x:c r="C38" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C38" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -42054,8 +42078,8 @@
       <x:c r="B39" s="9" t="str">
         <x:v>TCE</x:v>
       </x:c>
-      <x:c r="C39" s="9" t="str">
-        <x:v>Common Modules</x:v>
+      <x:c r="C39" s="9" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -42065,9 +42089,7 @@
       <x:c r="B40" s="9" t="str">
         <x:v>TITO</x:v>
       </x:c>
-      <x:c r="C40" s="9" t="str">
-        <x:v>Common Modules</x:v>
-      </x:c>
+      <x:c r="C40" s="9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
